--- a/P360_Config_Template.xlsx
+++ b/P360_Config_Template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R1696afc9b484486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="2" r:id="R5b57bc710285412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rbe720aead74c4a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="2" r:id="R4431bdc37d2f4b8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +45,14 @@
       <x:color rgb="FF2A1D12"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF8A552A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,65 +79,59 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2A1D12"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2A1D12"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2A1D12"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1E5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="16">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -243,6 +243,44 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -294,9 +332,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -487,6 +525,22 @@
         <x:v>Upload this workbook from the dashboard. Manually saved server rows are combined with uploaded Excel rows.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="34" customHeight="1">
+      <x:c r="A12" s="61" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="19" t="str">
+        <x:v>Optional: add comma-separated Affise Offer IDs for each app to enable the app-level Affise vs AppsFlyer overall-click comparison. Repeat the same offer IDs on that app's PID rows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="69" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="19" t="str">
+        <x:v>Optional: enter the exact, case-sensitive AppsFlyer Billable Event Name for each App + PID + PRT row. P360 counts only accepted raw in-app events; blocked-event reports and blocked-event postbacks are excluded.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -506,6 +560,8 @@
     <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -530,6 +586,12 @@
       <x:c r="G1" s="35" t="str">
         <x:v>Notes</x:v>
       </x:c>
+      <x:c r="H1" s="60" t="str">
+        <x:v>Affise Offer IDs</x:v>
+      </x:c>
+      <x:c r="I1" s="66" t="str">
+        <x:v>Billable Event Name</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="40" t="str">
@@ -553,6 +615,8 @@
       <x:c r="G2" s="50" t="str">
         <x:v>Example row</x:v>
       </x:c>
+      <x:c r="H2" t="str"/>
+      <x:c r="I2" t="str"/>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="40" t="str">
@@ -576,6 +640,8 @@
       <x:c r="G3" s="50" t="str">
         <x:v>Separate PID row</x:v>
       </x:c>
+      <x:c r="H3" t="str"/>
+      <x:c r="I3" t="str"/>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="40" t="str">
@@ -599,6 +665,8 @@
       <x:c r="G4" s="50" t="str">
         <x:v>Philippines timezone</x:v>
       </x:c>
+      <x:c r="H4" t="str"/>
+      <x:c r="I4" t="str"/>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="40" t="str">
@@ -622,6 +690,8 @@
       <x:c r="G5" s="50" t="str">
         <x:v>Indonesia timezone</x:v>
       </x:c>
+      <x:c r="H5" t="str"/>
+      <x:c r="I5" t="str"/>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="40" t="str">
@@ -635,6 +705,8 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G6" s="50" t="str"/>
+      <x:c r="H6" t="str"/>
+      <x:c r="I6" t="str"/>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="40" t="str">
@@ -648,6 +720,8 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G7" s="50" t="str"/>
+      <x:c r="H7" t="str"/>
+      <x:c r="I7" t="str"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="40" t="str">
@@ -661,6 +735,8 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G8" s="50" t="str"/>
+      <x:c r="H8" t="str"/>
+      <x:c r="I8" t="str"/>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="40"/>
@@ -670,6 +746,8 @@
       <x:c r="E9" s="46"/>
       <x:c r="F9" s="40"/>
       <x:c r="G9" s="50"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="40"/>
@@ -679,6 +757,8 @@
       <x:c r="E10" s="46"/>
       <x:c r="F10" s="40"/>
       <x:c r="G10" s="50"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="40"/>
@@ -688,6 +768,8 @@
       <x:c r="E11" s="46"/>
       <x:c r="F11" s="40"/>
       <x:c r="G11" s="50"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="40"/>
@@ -697,6 +779,8 @@
       <x:c r="E12" s="46"/>
       <x:c r="F12" s="40"/>
       <x:c r="G12" s="50"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="40"/>
@@ -706,6 +790,8 @@
       <x:c r="E13" s="46"/>
       <x:c r="F13" s="40"/>
       <x:c r="G13" s="50"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="40"/>
@@ -715,6 +801,8 @@
       <x:c r="E14" s="46"/>
       <x:c r="F14" s="40"/>
       <x:c r="G14" s="50"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="40"/>
@@ -724,6 +812,8 @@
       <x:c r="E15" s="46"/>
       <x:c r="F15" s="40"/>
       <x:c r="G15" s="50"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="40"/>
@@ -733,6 +823,8 @@
       <x:c r="E16" s="46"/>
       <x:c r="F16" s="40"/>
       <x:c r="G16" s="50"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="40"/>
@@ -742,6 +834,8 @@
       <x:c r="E17" s="46"/>
       <x:c r="F17" s="40"/>
       <x:c r="G17" s="50"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
       <x:c r="A18" s="40"/>
@@ -751,6 +845,8 @@
       <x:c r="E18" s="46"/>
       <x:c r="F18" s="40"/>
       <x:c r="G18" s="50"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="40"/>
@@ -760,6 +856,8 @@
       <x:c r="E19" s="46"/>
       <x:c r="F19" s="40"/>
       <x:c r="G19" s="50"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="40"/>
@@ -769,6 +867,8 @@
       <x:c r="E20" s="46"/>
       <x:c r="F20" s="40"/>
       <x:c r="G20" s="50"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="40"/>
@@ -778,6 +878,8 @@
       <x:c r="E21" s="46"/>
       <x:c r="F21" s="40"/>
       <x:c r="G21" s="50"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="40"/>
@@ -787,6 +889,8 @@
       <x:c r="E22" s="46"/>
       <x:c r="F22" s="40"/>
       <x:c r="G22" s="50"/>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="40"/>
@@ -796,6 +900,8 @@
       <x:c r="E23" s="46"/>
       <x:c r="F23" s="40"/>
       <x:c r="G23" s="50"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
       <x:c r="A24" s="40"/>
@@ -805,6 +911,8 @@
       <x:c r="E24" s="46"/>
       <x:c r="F24" s="40"/>
       <x:c r="G24" s="50"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
       <x:c r="A25" s="40"/>
@@ -814,6 +922,8 @@
       <x:c r="E25" s="46"/>
       <x:c r="F25" s="40"/>
       <x:c r="G25" s="50"/>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
       <x:c r="A26" s="40"/>
@@ -823,6 +933,8 @@
       <x:c r="E26" s="46"/>
       <x:c r="F26" s="40"/>
       <x:c r="G26" s="50"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="40"/>
@@ -832,6 +944,8 @@
       <x:c r="E27" s="46"/>
       <x:c r="F27" s="40"/>
       <x:c r="G27" s="50"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
       <x:c r="A28" s="40"/>
@@ -841,6 +955,8 @@
       <x:c r="E28" s="46"/>
       <x:c r="F28" s="40"/>
       <x:c r="G28" s="50"/>
+      <x:c r="H28"/>
+      <x:c r="I28"/>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
       <x:c r="A29" s="40"/>
@@ -850,6 +966,8 @@
       <x:c r="E29" s="46"/>
       <x:c r="F29" s="40"/>
       <x:c r="G29" s="50"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
       <x:c r="A30" s="40"/>
@@ -859,6 +977,8 @@
       <x:c r="E30" s="46"/>
       <x:c r="F30" s="40"/>
       <x:c r="G30" s="50"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
     </x:row>
     <x:row r="31" ht="23" customHeight="1">
       <x:c r="A31" s="40"/>
@@ -868,6 +988,8 @@
       <x:c r="E31" s="46"/>
       <x:c r="F31" s="40"/>
       <x:c r="G31" s="50"/>
+      <x:c r="H31"/>
+      <x:c r="I31"/>
     </x:row>
     <x:row r="32" ht="23" customHeight="1">
       <x:c r="A32" s="40"/>
@@ -877,6 +999,8 @@
       <x:c r="E32" s="46"/>
       <x:c r="F32" s="40"/>
       <x:c r="G32" s="50"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
     </x:row>
     <x:row r="33" ht="23" customHeight="1">
       <x:c r="A33" s="40"/>
@@ -886,6 +1010,8 @@
       <x:c r="E33" s="46"/>
       <x:c r="F33" s="40"/>
       <x:c r="G33" s="50"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
       <x:c r="A34" s="40"/>
@@ -895,6 +1021,8 @@
       <x:c r="E34" s="46"/>
       <x:c r="F34" s="40"/>
       <x:c r="G34" s="50"/>
+      <x:c r="H34"/>
+      <x:c r="I34"/>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
       <x:c r="A35" s="40"/>
@@ -904,6 +1032,8 @@
       <x:c r="E35" s="46"/>
       <x:c r="F35" s="40"/>
       <x:c r="G35" s="50"/>
+      <x:c r="H35"/>
+      <x:c r="I35"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="40"/>
@@ -913,6 +1043,8 @@
       <x:c r="E36" s="46"/>
       <x:c r="F36" s="40"/>
       <x:c r="G36" s="50"/>
+      <x:c r="H36"/>
+      <x:c r="I36"/>
     </x:row>
     <x:row r="37" ht="23" customHeight="1">
       <x:c r="A37" s="40"/>
@@ -922,6 +1054,8 @@
       <x:c r="E37" s="46"/>
       <x:c r="F37" s="40"/>
       <x:c r="G37" s="50"/>
+      <x:c r="H37"/>
+      <x:c r="I37"/>
     </x:row>
     <x:row r="38" ht="23" customHeight="1">
       <x:c r="A38" s="40"/>
@@ -931,6 +1065,8 @@
       <x:c r="E38" s="46"/>
       <x:c r="F38" s="40"/>
       <x:c r="G38" s="50"/>
+      <x:c r="H38"/>
+      <x:c r="I38"/>
     </x:row>
     <x:row r="39" ht="23" customHeight="1">
       <x:c r="A39" s="40"/>
@@ -940,6 +1076,8 @@
       <x:c r="E39" s="46"/>
       <x:c r="F39" s="40"/>
       <x:c r="G39" s="50"/>
+      <x:c r="H39"/>
+      <x:c r="I39"/>
     </x:row>
     <x:row r="40" ht="23" customHeight="1">
       <x:c r="A40" s="40"/>
@@ -949,6 +1087,8 @@
       <x:c r="E40" s="46"/>
       <x:c r="F40" s="40"/>
       <x:c r="G40" s="50"/>
+      <x:c r="H40"/>
+      <x:c r="I40"/>
     </x:row>
     <x:row r="41" ht="23" customHeight="1">
       <x:c r="A41" s="40"/>
@@ -958,6 +1098,8 @@
       <x:c r="E41" s="46"/>
       <x:c r="F41" s="40"/>
       <x:c r="G41" s="50"/>
+      <x:c r="H41"/>
+      <x:c r="I41"/>
     </x:row>
     <x:row r="42" ht="23" customHeight="1">
       <x:c r="A42" s="40"/>
@@ -967,6 +1109,8 @@
       <x:c r="E42" s="46"/>
       <x:c r="F42" s="40"/>
       <x:c r="G42" s="50"/>
+      <x:c r="H42"/>
+      <x:c r="I42"/>
     </x:row>
     <x:row r="43" ht="23" customHeight="1">
       <x:c r="A43" s="40"/>
@@ -976,6 +1120,8 @@
       <x:c r="E43" s="46"/>
       <x:c r="F43" s="40"/>
       <x:c r="G43" s="50"/>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
     </x:row>
     <x:row r="44" ht="23" customHeight="1">
       <x:c r="A44" s="40"/>
@@ -985,6 +1131,8 @@
       <x:c r="E44" s="46"/>
       <x:c r="F44" s="40"/>
       <x:c r="G44" s="50"/>
+      <x:c r="H44"/>
+      <x:c r="I44"/>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="40"/>
@@ -994,6 +1142,8 @@
       <x:c r="E45" s="46"/>
       <x:c r="F45" s="40"/>
       <x:c r="G45" s="50"/>
+      <x:c r="H45"/>
+      <x:c r="I45"/>
     </x:row>
     <x:row r="46" ht="23" customHeight="1">
       <x:c r="A46" s="40"/>
@@ -1003,6 +1153,8 @@
       <x:c r="E46" s="46"/>
       <x:c r="F46" s="40"/>
       <x:c r="G46" s="50"/>
+      <x:c r="H46"/>
+      <x:c r="I46"/>
     </x:row>
     <x:row r="47" ht="23" customHeight="1">
       <x:c r="A47" s="40"/>
@@ -1012,6 +1164,8 @@
       <x:c r="E47" s="46"/>
       <x:c r="F47" s="40"/>
       <x:c r="G47" s="50"/>
+      <x:c r="H47"/>
+      <x:c r="I47"/>
     </x:row>
     <x:row r="48" ht="23" customHeight="1">
       <x:c r="A48" s="40"/>
@@ -1021,6 +1175,8 @@
       <x:c r="E48" s="46"/>
       <x:c r="F48" s="40"/>
       <x:c r="G48" s="50"/>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
     </x:row>
     <x:row r="49" ht="23" customHeight="1">
       <x:c r="A49" s="40"/>
@@ -1030,6 +1186,8 @@
       <x:c r="E49" s="46"/>
       <x:c r="F49" s="40"/>
       <x:c r="G49" s="50"/>
+      <x:c r="H49"/>
+      <x:c r="I49"/>
     </x:row>
     <x:row r="50" ht="23" customHeight="1">
       <x:c r="A50" s="40"/>
@@ -1039,6 +1197,8 @@
       <x:c r="E50" s="46"/>
       <x:c r="F50" s="40"/>
       <x:c r="G50" s="50"/>
+      <x:c r="H50"/>
+      <x:c r="I50"/>
     </x:row>
     <x:row r="51" ht="23" customHeight="1">
       <x:c r="A51" s="40"/>
@@ -1048,6 +1208,8 @@
       <x:c r="E51" s="46"/>
       <x:c r="F51" s="40"/>
       <x:c r="G51" s="50"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
     </x:row>
     <x:row r="52" ht="23" customHeight="1">
       <x:c r="A52" s="40"/>
@@ -1057,6 +1219,8 @@
       <x:c r="E52" s="46"/>
       <x:c r="F52" s="40"/>
       <x:c r="G52" s="50"/>
+      <x:c r="H52"/>
+      <x:c r="I52"/>
     </x:row>
     <x:row r="53" ht="23" customHeight="1">
       <x:c r="A53" s="40"/>
@@ -1066,6 +1230,8 @@
       <x:c r="E53" s="46"/>
       <x:c r="F53" s="40"/>
       <x:c r="G53" s="50"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
     </x:row>
     <x:row r="54" ht="23" customHeight="1">
       <x:c r="A54" s="40"/>
@@ -1075,6 +1241,8 @@
       <x:c r="E54" s="46"/>
       <x:c r="F54" s="40"/>
       <x:c r="G54" s="50"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
     </x:row>
     <x:row r="55" ht="23" customHeight="1">
       <x:c r="A55" s="40"/>
@@ -1084,6 +1252,8 @@
       <x:c r="E55" s="46"/>
       <x:c r="F55" s="40"/>
       <x:c r="G55" s="50"/>
+      <x:c r="H55"/>
+      <x:c r="I55"/>
     </x:row>
     <x:row r="56" ht="23" customHeight="1">
       <x:c r="A56" s="40"/>
@@ -1093,6 +1263,8 @@
       <x:c r="E56" s="46"/>
       <x:c r="F56" s="40"/>
       <x:c r="G56" s="50"/>
+      <x:c r="H56"/>
+      <x:c r="I56"/>
     </x:row>
     <x:row r="57" ht="23" customHeight="1">
       <x:c r="A57" s="40"/>
@@ -1102,6 +1274,8 @@
       <x:c r="E57" s="46"/>
       <x:c r="F57" s="40"/>
       <x:c r="G57" s="50"/>
+      <x:c r="H57"/>
+      <x:c r="I57"/>
     </x:row>
     <x:row r="58" ht="23" customHeight="1">
       <x:c r="A58" s="40"/>
@@ -1111,6 +1285,8 @@
       <x:c r="E58" s="46"/>
       <x:c r="F58" s="40"/>
       <x:c r="G58" s="50"/>
+      <x:c r="H58"/>
+      <x:c r="I58"/>
     </x:row>
     <x:row r="59" ht="23" customHeight="1">
       <x:c r="A59" s="40"/>
@@ -1120,6 +1296,8 @@
       <x:c r="E59" s="46"/>
       <x:c r="F59" s="40"/>
       <x:c r="G59" s="50"/>
+      <x:c r="H59"/>
+      <x:c r="I59"/>
     </x:row>
     <x:row r="60" ht="23" customHeight="1">
       <x:c r="A60" s="40"/>
@@ -1129,6 +1307,8 @@
       <x:c r="E60" s="46"/>
       <x:c r="F60" s="40"/>
       <x:c r="G60" s="50"/>
+      <x:c r="H60"/>
+      <x:c r="I60"/>
     </x:row>
     <x:row r="61" ht="23" customHeight="1">
       <x:c r="A61" s="40"/>
@@ -1138,6 +1318,8 @@
       <x:c r="E61" s="46"/>
       <x:c r="F61" s="40"/>
       <x:c r="G61" s="50"/>
+      <x:c r="H61"/>
+      <x:c r="I61"/>
     </x:row>
     <x:row r="62" ht="23" customHeight="1">
       <x:c r="A62" s="40"/>
@@ -1147,6 +1329,8 @@
       <x:c r="E62" s="46"/>
       <x:c r="F62" s="40"/>
       <x:c r="G62" s="50"/>
+      <x:c r="H62"/>
+      <x:c r="I62"/>
     </x:row>
     <x:row r="63" ht="23" customHeight="1">
       <x:c r="A63" s="40"/>
@@ -1156,6 +1340,8 @@
       <x:c r="E63" s="46"/>
       <x:c r="F63" s="40"/>
       <x:c r="G63" s="50"/>
+      <x:c r="H63"/>
+      <x:c r="I63"/>
     </x:row>
     <x:row r="64" ht="23" customHeight="1">
       <x:c r="A64" s="40"/>
@@ -1165,6 +1351,8 @@
       <x:c r="E64" s="46"/>
       <x:c r="F64" s="40"/>
       <x:c r="G64" s="50"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
     </x:row>
     <x:row r="65" ht="23" customHeight="1">
       <x:c r="A65" s="40"/>
@@ -1174,6 +1362,8 @@
       <x:c r="E65" s="46"/>
       <x:c r="F65" s="40"/>
       <x:c r="G65" s="50"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
     </x:row>
     <x:row r="66" ht="23" customHeight="1">
       <x:c r="A66" s="40"/>
@@ -1183,6 +1373,8 @@
       <x:c r="E66" s="46"/>
       <x:c r="F66" s="40"/>
       <x:c r="G66" s="50"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
     </x:row>
     <x:row r="67" ht="23" customHeight="1">
       <x:c r="A67" s="40"/>
@@ -1192,6 +1384,8 @@
       <x:c r="E67" s="46"/>
       <x:c r="F67" s="40"/>
       <x:c r="G67" s="50"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
     </x:row>
     <x:row r="68" ht="23" customHeight="1">
       <x:c r="A68" s="40"/>
@@ -1201,6 +1395,8 @@
       <x:c r="E68" s="46"/>
       <x:c r="F68" s="40"/>
       <x:c r="G68" s="50"/>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="40"/>
@@ -1210,6 +1406,8 @@
       <x:c r="E69" s="46"/>
       <x:c r="F69" s="40"/>
       <x:c r="G69" s="50"/>
+      <x:c r="H69"/>
+      <x:c r="I69"/>
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="40"/>
@@ -1219,6 +1417,8 @@
       <x:c r="E70" s="46"/>
       <x:c r="F70" s="40"/>
       <x:c r="G70" s="50"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="40"/>
@@ -1228,6 +1428,8 @@
       <x:c r="E71" s="46"/>
       <x:c r="F71" s="40"/>
       <x:c r="G71" s="50"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="40"/>
@@ -1237,6 +1439,8 @@
       <x:c r="E72" s="46"/>
       <x:c r="F72" s="40"/>
       <x:c r="G72" s="50"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="40"/>
@@ -1246,6 +1450,8 @@
       <x:c r="E73" s="46"/>
       <x:c r="F73" s="40"/>
       <x:c r="G73" s="50"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="40"/>
@@ -1255,6 +1461,8 @@
       <x:c r="E74" s="46"/>
       <x:c r="F74" s="40"/>
       <x:c r="G74" s="50"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="40"/>
@@ -1264,6 +1472,8 @@
       <x:c r="E75" s="46"/>
       <x:c r="F75" s="40"/>
       <x:c r="G75" s="50"/>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="40"/>
@@ -1273,6 +1483,8 @@
       <x:c r="E76" s="46"/>
       <x:c r="F76" s="40"/>
       <x:c r="G76" s="50"/>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="40"/>
@@ -1282,6 +1494,8 @@
       <x:c r="E77" s="46"/>
       <x:c r="F77" s="40"/>
       <x:c r="G77" s="50"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="40"/>
@@ -1291,6 +1505,8 @@
       <x:c r="E78" s="46"/>
       <x:c r="F78" s="40"/>
       <x:c r="G78" s="50"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="40"/>
@@ -1300,6 +1516,8 @@
       <x:c r="E79" s="46"/>
       <x:c r="F79" s="40"/>
       <x:c r="G79" s="50"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="40"/>
@@ -1309,6 +1527,8 @@
       <x:c r="E80" s="46"/>
       <x:c r="F80" s="40"/>
       <x:c r="G80" s="50"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="40"/>
@@ -1318,6 +1538,8 @@
       <x:c r="E81" s="46"/>
       <x:c r="F81" s="40"/>
       <x:c r="G81" s="50"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="40"/>
@@ -1327,6 +1549,8 @@
       <x:c r="E82" s="46"/>
       <x:c r="F82" s="40"/>
       <x:c r="G82" s="50"/>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="40"/>
@@ -1336,6 +1560,8 @@
       <x:c r="E83" s="46"/>
       <x:c r="F83" s="40"/>
       <x:c r="G83" s="50"/>
+      <x:c r="H83"/>
+      <x:c r="I83"/>
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="40"/>
@@ -1345,6 +1571,8 @@
       <x:c r="E84" s="46"/>
       <x:c r="F84" s="40"/>
       <x:c r="G84" s="50"/>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="40"/>
@@ -1354,6 +1582,8 @@
       <x:c r="E85" s="46"/>
       <x:c r="F85" s="40"/>
       <x:c r="G85" s="50"/>
+      <x:c r="H85"/>
+      <x:c r="I85"/>
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="40"/>
@@ -1363,6 +1593,8 @@
       <x:c r="E86" s="46"/>
       <x:c r="F86" s="40"/>
       <x:c r="G86" s="50"/>
+      <x:c r="H86"/>
+      <x:c r="I86"/>
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="40"/>
@@ -1372,6 +1604,8 @@
       <x:c r="E87" s="46"/>
       <x:c r="F87" s="40"/>
       <x:c r="G87" s="50"/>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="40"/>
@@ -1381,6 +1615,8 @@
       <x:c r="E88" s="46"/>
       <x:c r="F88" s="40"/>
       <x:c r="G88" s="50"/>
+      <x:c r="H88"/>
+      <x:c r="I88"/>
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="40"/>
@@ -1390,6 +1626,8 @@
       <x:c r="E89" s="46"/>
       <x:c r="F89" s="40"/>
       <x:c r="G89" s="50"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="40"/>
@@ -1399,6 +1637,8 @@
       <x:c r="E90" s="46"/>
       <x:c r="F90" s="40"/>
       <x:c r="G90" s="50"/>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="40"/>
@@ -1408,6 +1648,8 @@
       <x:c r="E91" s="46"/>
       <x:c r="F91" s="40"/>
       <x:c r="G91" s="50"/>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="40"/>
@@ -1417,6 +1659,8 @@
       <x:c r="E92" s="46"/>
       <x:c r="F92" s="40"/>
       <x:c r="G92" s="50"/>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="40"/>
@@ -1426,6 +1670,8 @@
       <x:c r="E93" s="46"/>
       <x:c r="F93" s="40"/>
       <x:c r="G93" s="50"/>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="40"/>
@@ -1435,6 +1681,8 @@
       <x:c r="E94" s="46"/>
       <x:c r="F94" s="40"/>
       <x:c r="G94" s="50"/>
+      <x:c r="H94"/>
+      <x:c r="I94"/>
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="40"/>
@@ -1444,6 +1692,8 @@
       <x:c r="E95" s="46"/>
       <x:c r="F95" s="40"/>
       <x:c r="G95" s="50"/>
+      <x:c r="H95"/>
+      <x:c r="I95"/>
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="40"/>
@@ -1453,6 +1703,8 @@
       <x:c r="E96" s="46"/>
       <x:c r="F96" s="40"/>
       <x:c r="G96" s="50"/>
+      <x:c r="H96"/>
+      <x:c r="I96"/>
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="40"/>
@@ -1462,6 +1714,8 @@
       <x:c r="E97" s="46"/>
       <x:c r="F97" s="40"/>
       <x:c r="G97" s="50"/>
+      <x:c r="H97"/>
+      <x:c r="I97"/>
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="40"/>
@@ -1471,6 +1725,8 @@
       <x:c r="E98" s="46"/>
       <x:c r="F98" s="40"/>
       <x:c r="G98" s="50"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="40"/>
@@ -1480,6 +1736,8 @@
       <x:c r="E99" s="46"/>
       <x:c r="F99" s="40"/>
       <x:c r="G99" s="50"/>
+      <x:c r="H99"/>
+      <x:c r="I99"/>
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="40"/>
@@ -1489,6 +1747,8 @@
       <x:c r="E100" s="46"/>
       <x:c r="F100" s="40"/>
       <x:c r="G100" s="50"/>
+      <x:c r="H100"/>
+      <x:c r="I100"/>
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="40"/>
@@ -1498,6 +1758,8 @@
       <x:c r="E101" s="46"/>
       <x:c r="F101" s="40"/>
       <x:c r="G101" s="50"/>
+      <x:c r="H101"/>
+      <x:c r="I101"/>
     </x:row>
     <x:row r="102" ht="23" customHeight="1">
       <x:c r="A102" s="40"/>
@@ -1507,6 +1769,8 @@
       <x:c r="E102" s="46"/>
       <x:c r="F102" s="40"/>
       <x:c r="G102" s="50"/>
+      <x:c r="H102"/>
+      <x:c r="I102"/>
     </x:row>
     <x:row r="103" ht="23" customHeight="1">
       <x:c r="A103" s="40"/>
@@ -1516,6 +1780,8 @@
       <x:c r="E103" s="46"/>
       <x:c r="F103" s="40"/>
       <x:c r="G103" s="50"/>
+      <x:c r="H103"/>
+      <x:c r="I103"/>
     </x:row>
     <x:row r="104" ht="23" customHeight="1">
       <x:c r="A104" s="40"/>
@@ -1525,6 +1791,8 @@
       <x:c r="E104" s="46"/>
       <x:c r="F104" s="40"/>
       <x:c r="G104" s="50"/>
+      <x:c r="H104"/>
+      <x:c r="I104"/>
     </x:row>
     <x:row r="105" ht="23" customHeight="1">
       <x:c r="A105" s="40"/>
@@ -1534,6 +1802,8 @@
       <x:c r="E105" s="46"/>
       <x:c r="F105" s="40"/>
       <x:c r="G105" s="50"/>
+      <x:c r="H105"/>
+      <x:c r="I105"/>
     </x:row>
     <x:row r="106" ht="23" customHeight="1">
       <x:c r="A106" s="40"/>
@@ -1543,6 +1813,8 @@
       <x:c r="E106" s="46"/>
       <x:c r="F106" s="40"/>
       <x:c r="G106" s="50"/>
+      <x:c r="H106"/>
+      <x:c r="I106"/>
     </x:row>
     <x:row r="107" ht="23" customHeight="1">
       <x:c r="A107" s="40"/>
@@ -1552,6 +1824,8 @@
       <x:c r="E107" s="46"/>
       <x:c r="F107" s="40"/>
       <x:c r="G107" s="50"/>
+      <x:c r="H107"/>
+      <x:c r="I107"/>
     </x:row>
     <x:row r="108" ht="23" customHeight="1">
       <x:c r="A108" s="40"/>
@@ -1561,6 +1835,8 @@
       <x:c r="E108" s="46"/>
       <x:c r="F108" s="40"/>
       <x:c r="G108" s="50"/>
+      <x:c r="H108"/>
+      <x:c r="I108"/>
     </x:row>
     <x:row r="109" ht="23" customHeight="1">
       <x:c r="A109" s="40"/>
@@ -1570,6 +1846,8 @@
       <x:c r="E109" s="46"/>
       <x:c r="F109" s="40"/>
       <x:c r="G109" s="50"/>
+      <x:c r="H109"/>
+      <x:c r="I109"/>
     </x:row>
     <x:row r="110" ht="23" customHeight="1">
       <x:c r="A110" s="40"/>
@@ -1579,6 +1857,8 @@
       <x:c r="E110" s="46"/>
       <x:c r="F110" s="40"/>
       <x:c r="G110" s="50"/>
+      <x:c r="H110"/>
+      <x:c r="I110"/>
     </x:row>
     <x:row r="111" ht="23" customHeight="1">
       <x:c r="A111" s="40"/>
@@ -1588,6 +1868,8 @@
       <x:c r="E111" s="46"/>
       <x:c r="F111" s="40"/>
       <x:c r="G111" s="50"/>
+      <x:c r="H111"/>
+      <x:c r="I111"/>
     </x:row>
     <x:row r="112" ht="23" customHeight="1">
       <x:c r="A112" s="40"/>
@@ -1597,6 +1879,8 @@
       <x:c r="E112" s="46"/>
       <x:c r="F112" s="40"/>
       <x:c r="G112" s="50"/>
+      <x:c r="H112"/>
+      <x:c r="I112"/>
     </x:row>
     <x:row r="113" ht="23" customHeight="1">
       <x:c r="A113" s="40"/>
@@ -1606,6 +1890,8 @@
       <x:c r="E113" s="46"/>
       <x:c r="F113" s="40"/>
       <x:c r="G113" s="50"/>
+      <x:c r="H113"/>
+      <x:c r="I113"/>
     </x:row>
     <x:row r="114" ht="23" customHeight="1">
       <x:c r="A114" s="40"/>
@@ -1615,6 +1901,8 @@
       <x:c r="E114" s="46"/>
       <x:c r="F114" s="40"/>
       <x:c r="G114" s="50"/>
+      <x:c r="H114"/>
+      <x:c r="I114"/>
     </x:row>
     <x:row r="115" ht="23" customHeight="1">
       <x:c r="A115" s="40"/>
@@ -1624,6 +1912,8 @@
       <x:c r="E115" s="46"/>
       <x:c r="F115" s="40"/>
       <x:c r="G115" s="50"/>
+      <x:c r="H115"/>
+      <x:c r="I115"/>
     </x:row>
     <x:row r="116" ht="23" customHeight="1">
       <x:c r="A116" s="40"/>
@@ -1633,6 +1923,8 @@
       <x:c r="E116" s="46"/>
       <x:c r="F116" s="40"/>
       <x:c r="G116" s="50"/>
+      <x:c r="H116"/>
+      <x:c r="I116"/>
     </x:row>
     <x:row r="117" ht="23" customHeight="1">
       <x:c r="A117" s="40"/>
@@ -1642,6 +1934,8 @@
       <x:c r="E117" s="46"/>
       <x:c r="F117" s="40"/>
       <x:c r="G117" s="50"/>
+      <x:c r="H117"/>
+      <x:c r="I117"/>
     </x:row>
     <x:row r="118" ht="23" customHeight="1">
       <x:c r="A118" s="40"/>
@@ -1651,6 +1945,8 @@
       <x:c r="E118" s="46"/>
       <x:c r="F118" s="40"/>
       <x:c r="G118" s="50"/>
+      <x:c r="H118"/>
+      <x:c r="I118"/>
     </x:row>
     <x:row r="119" ht="23" customHeight="1">
       <x:c r="A119" s="40"/>
@@ -1660,6 +1956,8 @@
       <x:c r="E119" s="46"/>
       <x:c r="F119" s="40"/>
       <x:c r="G119" s="50"/>
+      <x:c r="H119"/>
+      <x:c r="I119"/>
     </x:row>
     <x:row r="120" ht="23" customHeight="1">
       <x:c r="A120" s="40"/>
@@ -1669,6 +1967,8 @@
       <x:c r="E120" s="46"/>
       <x:c r="F120" s="40"/>
       <x:c r="G120" s="50"/>
+      <x:c r="H120"/>
+      <x:c r="I120"/>
     </x:row>
     <x:row r="121" ht="23" customHeight="1">
       <x:c r="A121" s="40"/>
@@ -1678,6 +1978,8 @@
       <x:c r="E121" s="46"/>
       <x:c r="F121" s="40"/>
       <x:c r="G121" s="50"/>
+      <x:c r="H121"/>
+      <x:c r="I121"/>
     </x:row>
     <x:row r="122" ht="23" customHeight="1">
       <x:c r="A122" s="40"/>
@@ -1687,6 +1989,8 @@
       <x:c r="E122" s="46"/>
       <x:c r="F122" s="40"/>
       <x:c r="G122" s="50"/>
+      <x:c r="H122"/>
+      <x:c r="I122"/>
     </x:row>
     <x:row r="123" ht="23" customHeight="1">
       <x:c r="A123" s="40"/>
@@ -1696,6 +2000,8 @@
       <x:c r="E123" s="46"/>
       <x:c r="F123" s="40"/>
       <x:c r="G123" s="50"/>
+      <x:c r="H123"/>
+      <x:c r="I123"/>
     </x:row>
     <x:row r="124" ht="23" customHeight="1">
       <x:c r="A124" s="40"/>
@@ -1705,6 +2011,8 @@
       <x:c r="E124" s="46"/>
       <x:c r="F124" s="40"/>
       <x:c r="G124" s="50"/>
+      <x:c r="H124"/>
+      <x:c r="I124"/>
     </x:row>
     <x:row r="125" ht="23" customHeight="1">
       <x:c r="A125" s="40"/>
@@ -1714,6 +2022,8 @@
       <x:c r="E125" s="46"/>
       <x:c r="F125" s="40"/>
       <x:c r="G125" s="50"/>
+      <x:c r="H125"/>
+      <x:c r="I125"/>
     </x:row>
     <x:row r="126" ht="23" customHeight="1">
       <x:c r="A126" s="40"/>
@@ -1723,6 +2033,8 @@
       <x:c r="E126" s="46"/>
       <x:c r="F126" s="40"/>
       <x:c r="G126" s="50"/>
+      <x:c r="H126"/>
+      <x:c r="I126"/>
     </x:row>
     <x:row r="127" ht="23" customHeight="1">
       <x:c r="A127" s="40"/>
@@ -1732,6 +2044,8 @@
       <x:c r="E127" s="46"/>
       <x:c r="F127" s="40"/>
       <x:c r="G127" s="50"/>
+      <x:c r="H127"/>
+      <x:c r="I127"/>
     </x:row>
     <x:row r="128" ht="23" customHeight="1">
       <x:c r="A128" s="40"/>
@@ -1741,6 +2055,8 @@
       <x:c r="E128" s="46"/>
       <x:c r="F128" s="40"/>
       <x:c r="G128" s="50"/>
+      <x:c r="H128"/>
+      <x:c r="I128"/>
     </x:row>
     <x:row r="129" ht="23" customHeight="1">
       <x:c r="A129" s="40"/>
@@ -1750,6 +2066,8 @@
       <x:c r="E129" s="46"/>
       <x:c r="F129" s="40"/>
       <x:c r="G129" s="50"/>
+      <x:c r="H129"/>
+      <x:c r="I129"/>
     </x:row>
     <x:row r="130" ht="23" customHeight="1">
       <x:c r="A130" s="40"/>
@@ -1759,6 +2077,8 @@
       <x:c r="E130" s="46"/>
       <x:c r="F130" s="40"/>
       <x:c r="G130" s="50"/>
+      <x:c r="H130"/>
+      <x:c r="I130"/>
     </x:row>
     <x:row r="131" ht="23" customHeight="1">
       <x:c r="A131" s="40"/>
@@ -1768,6 +2088,8 @@
       <x:c r="E131" s="46"/>
       <x:c r="F131" s="40"/>
       <x:c r="G131" s="50"/>
+      <x:c r="H131"/>
+      <x:c r="I131"/>
     </x:row>
     <x:row r="132" ht="23" customHeight="1">
       <x:c r="A132" s="40"/>
@@ -1777,6 +2099,8 @@
       <x:c r="E132" s="46"/>
       <x:c r="F132" s="40"/>
       <x:c r="G132" s="50"/>
+      <x:c r="H132"/>
+      <x:c r="I132"/>
     </x:row>
     <x:row r="133" ht="23" customHeight="1">
       <x:c r="A133" s="40"/>
@@ -1786,6 +2110,8 @@
       <x:c r="E133" s="46"/>
       <x:c r="F133" s="40"/>
       <x:c r="G133" s="50"/>
+      <x:c r="H133"/>
+      <x:c r="I133"/>
     </x:row>
     <x:row r="134" ht="23" customHeight="1">
       <x:c r="A134" s="40"/>
@@ -1795,6 +2121,8 @@
       <x:c r="E134" s="46"/>
       <x:c r="F134" s="40"/>
       <x:c r="G134" s="50"/>
+      <x:c r="H134"/>
+      <x:c r="I134"/>
     </x:row>
     <x:row r="135" ht="23" customHeight="1">
       <x:c r="A135" s="40"/>
@@ -1804,6 +2132,8 @@
       <x:c r="E135" s="46"/>
       <x:c r="F135" s="40"/>
       <x:c r="G135" s="50"/>
+      <x:c r="H135"/>
+      <x:c r="I135"/>
     </x:row>
     <x:row r="136" ht="23" customHeight="1">
       <x:c r="A136" s="40"/>
@@ -1813,6 +2143,8 @@
       <x:c r="E136" s="46"/>
       <x:c r="F136" s="40"/>
       <x:c r="G136" s="50"/>
+      <x:c r="H136"/>
+      <x:c r="I136"/>
     </x:row>
     <x:row r="137" ht="23" customHeight="1">
       <x:c r="A137" s="40"/>
@@ -1822,6 +2154,8 @@
       <x:c r="E137" s="46"/>
       <x:c r="F137" s="40"/>
       <x:c r="G137" s="50"/>
+      <x:c r="H137"/>
+      <x:c r="I137"/>
     </x:row>
     <x:row r="138" ht="23" customHeight="1">
       <x:c r="A138" s="40"/>
@@ -1831,6 +2165,8 @@
       <x:c r="E138" s="46"/>
       <x:c r="F138" s="40"/>
       <x:c r="G138" s="50"/>
+      <x:c r="H138"/>
+      <x:c r="I138"/>
     </x:row>
     <x:row r="139" ht="23" customHeight="1">
       <x:c r="A139" s="40"/>
@@ -1840,6 +2176,8 @@
       <x:c r="E139" s="46"/>
       <x:c r="F139" s="40"/>
       <x:c r="G139" s="50"/>
+      <x:c r="H139"/>
+      <x:c r="I139"/>
     </x:row>
     <x:row r="140" ht="23" customHeight="1">
       <x:c r="A140" s="40"/>
@@ -1849,6 +2187,8 @@
       <x:c r="E140" s="46"/>
       <x:c r="F140" s="40"/>
       <x:c r="G140" s="50"/>
+      <x:c r="H140"/>
+      <x:c r="I140"/>
     </x:row>
     <x:row r="141" ht="23" customHeight="1">
       <x:c r="A141" s="40"/>
@@ -1858,6 +2198,8 @@
       <x:c r="E141" s="46"/>
       <x:c r="F141" s="40"/>
       <x:c r="G141" s="50"/>
+      <x:c r="H141"/>
+      <x:c r="I141"/>
     </x:row>
     <x:row r="142" ht="23" customHeight="1">
       <x:c r="A142" s="40"/>
@@ -1867,6 +2209,8 @@
       <x:c r="E142" s="46"/>
       <x:c r="F142" s="40"/>
       <x:c r="G142" s="50"/>
+      <x:c r="H142"/>
+      <x:c r="I142"/>
     </x:row>
     <x:row r="143" ht="23" customHeight="1">
       <x:c r="A143" s="40"/>
@@ -1876,6 +2220,8 @@
       <x:c r="E143" s="46"/>
       <x:c r="F143" s="40"/>
       <x:c r="G143" s="50"/>
+      <x:c r="H143"/>
+      <x:c r="I143"/>
     </x:row>
     <x:row r="144" ht="23" customHeight="1">
       <x:c r="A144" s="40"/>
@@ -1885,6 +2231,8 @@
       <x:c r="E144" s="46"/>
       <x:c r="F144" s="40"/>
       <x:c r="G144" s="50"/>
+      <x:c r="H144"/>
+      <x:c r="I144"/>
     </x:row>
     <x:row r="145" ht="23" customHeight="1">
       <x:c r="A145" s="40"/>
@@ -1894,6 +2242,8 @@
       <x:c r="E145" s="46"/>
       <x:c r="F145" s="40"/>
       <x:c r="G145" s="50"/>
+      <x:c r="H145"/>
+      <x:c r="I145"/>
     </x:row>
     <x:row r="146" ht="23" customHeight="1">
       <x:c r="A146" s="40"/>
@@ -1903,6 +2253,8 @@
       <x:c r="E146" s="46"/>
       <x:c r="F146" s="40"/>
       <x:c r="G146" s="50"/>
+      <x:c r="H146"/>
+      <x:c r="I146"/>
     </x:row>
     <x:row r="147" ht="23" customHeight="1">
       <x:c r="A147" s="40"/>
@@ -1912,6 +2264,8 @@
       <x:c r="E147" s="46"/>
       <x:c r="F147" s="40"/>
       <x:c r="G147" s="50"/>
+      <x:c r="H147"/>
+      <x:c r="I147"/>
     </x:row>
     <x:row r="148" ht="23" customHeight="1">
       <x:c r="A148" s="40"/>
@@ -1921,6 +2275,8 @@
       <x:c r="E148" s="46"/>
       <x:c r="F148" s="40"/>
       <x:c r="G148" s="50"/>
+      <x:c r="H148"/>
+      <x:c r="I148"/>
     </x:row>
     <x:row r="149" ht="23" customHeight="1">
       <x:c r="A149" s="40"/>
@@ -1930,6 +2286,8 @@
       <x:c r="E149" s="46"/>
       <x:c r="F149" s="40"/>
       <x:c r="G149" s="50"/>
+      <x:c r="H149"/>
+      <x:c r="I149"/>
     </x:row>
     <x:row r="150" ht="23" customHeight="1">
       <x:c r="A150" s="40"/>
@@ -1939,6 +2297,8 @@
       <x:c r="E150" s="46"/>
       <x:c r="F150" s="40"/>
       <x:c r="G150" s="50"/>
+      <x:c r="H150"/>
+      <x:c r="I150"/>
     </x:row>
     <x:row r="151" ht="23" customHeight="1">
       <x:c r="A151" s="40"/>
@@ -1948,6 +2308,8 @@
       <x:c r="E151" s="46"/>
       <x:c r="F151" s="40"/>
       <x:c r="G151" s="50"/>
+      <x:c r="H151"/>
+      <x:c r="I151"/>
     </x:row>
     <x:row r="152" ht="23" customHeight="1">
       <x:c r="A152" s="40"/>
@@ -1957,6 +2319,8 @@
       <x:c r="E152" s="46"/>
       <x:c r="F152" s="40"/>
       <x:c r="G152" s="50"/>
+      <x:c r="H152"/>
+      <x:c r="I152"/>
     </x:row>
     <x:row r="153" ht="23" customHeight="1">
       <x:c r="A153" s="40"/>
@@ -1966,6 +2330,8 @@
       <x:c r="E153" s="46"/>
       <x:c r="F153" s="40"/>
       <x:c r="G153" s="50"/>
+      <x:c r="H153"/>
+      <x:c r="I153"/>
     </x:row>
     <x:row r="154" ht="23" customHeight="1">
       <x:c r="A154" s="40"/>
@@ -1975,6 +2341,8 @@
       <x:c r="E154" s="46"/>
       <x:c r="F154" s="40"/>
       <x:c r="G154" s="50"/>
+      <x:c r="H154"/>
+      <x:c r="I154"/>
     </x:row>
     <x:row r="155" ht="23" customHeight="1">
       <x:c r="A155" s="40"/>
@@ -1984,6 +2352,8 @@
       <x:c r="E155" s="46"/>
       <x:c r="F155" s="40"/>
       <x:c r="G155" s="50"/>
+      <x:c r="H155"/>
+      <x:c r="I155"/>
     </x:row>
     <x:row r="156" ht="23" customHeight="1">
       <x:c r="A156" s="40"/>
@@ -1993,6 +2363,8 @@
       <x:c r="E156" s="46"/>
       <x:c r="F156" s="40"/>
       <x:c r="G156" s="50"/>
+      <x:c r="H156"/>
+      <x:c r="I156"/>
     </x:row>
     <x:row r="157" ht="23" customHeight="1">
       <x:c r="A157" s="40"/>
@@ -2002,6 +2374,8 @@
       <x:c r="E157" s="46"/>
       <x:c r="F157" s="40"/>
       <x:c r="G157" s="50"/>
+      <x:c r="H157"/>
+      <x:c r="I157"/>
     </x:row>
     <x:row r="158" ht="23" customHeight="1">
       <x:c r="A158" s="40"/>
@@ -2011,6 +2385,8 @@
       <x:c r="E158" s="46"/>
       <x:c r="F158" s="40"/>
       <x:c r="G158" s="50"/>
+      <x:c r="H158"/>
+      <x:c r="I158"/>
     </x:row>
     <x:row r="159" ht="23" customHeight="1">
       <x:c r="A159" s="40"/>
@@ -2020,6 +2396,8 @@
       <x:c r="E159" s="46"/>
       <x:c r="F159" s="40"/>
       <x:c r="G159" s="50"/>
+      <x:c r="H159"/>
+      <x:c r="I159"/>
     </x:row>
     <x:row r="160" ht="23" customHeight="1">
       <x:c r="A160" s="40"/>
@@ -2029,6 +2407,8 @@
       <x:c r="E160" s="46"/>
       <x:c r="F160" s="40"/>
       <x:c r="G160" s="50"/>
+      <x:c r="H160"/>
+      <x:c r="I160"/>
     </x:row>
     <x:row r="161" ht="23" customHeight="1">
       <x:c r="A161" s="40"/>
@@ -2038,6 +2418,8 @@
       <x:c r="E161" s="46"/>
       <x:c r="F161" s="40"/>
       <x:c r="G161" s="50"/>
+      <x:c r="H161"/>
+      <x:c r="I161"/>
     </x:row>
     <x:row r="162" ht="23" customHeight="1">
       <x:c r="A162" s="40"/>
@@ -2047,6 +2429,8 @@
       <x:c r="E162" s="46"/>
       <x:c r="F162" s="40"/>
       <x:c r="G162" s="50"/>
+      <x:c r="H162"/>
+      <x:c r="I162"/>
     </x:row>
     <x:row r="163" ht="23" customHeight="1">
       <x:c r="A163" s="40"/>
@@ -2056,6 +2440,8 @@
       <x:c r="E163" s="46"/>
       <x:c r="F163" s="40"/>
       <x:c r="G163" s="50"/>
+      <x:c r="H163"/>
+      <x:c r="I163"/>
     </x:row>
     <x:row r="164" ht="23" customHeight="1">
       <x:c r="A164" s="40"/>
@@ -2065,6 +2451,8 @@
       <x:c r="E164" s="46"/>
       <x:c r="F164" s="40"/>
       <x:c r="G164" s="50"/>
+      <x:c r="H164"/>
+      <x:c r="I164"/>
     </x:row>
     <x:row r="165" ht="23" customHeight="1">
       <x:c r="A165" s="40"/>
@@ -2074,6 +2462,8 @@
       <x:c r="E165" s="46"/>
       <x:c r="F165" s="40"/>
       <x:c r="G165" s="50"/>
+      <x:c r="H165"/>
+      <x:c r="I165"/>
     </x:row>
     <x:row r="166" ht="23" customHeight="1">
       <x:c r="A166" s="40"/>
@@ -2083,6 +2473,8 @@
       <x:c r="E166" s="46"/>
       <x:c r="F166" s="40"/>
       <x:c r="G166" s="50"/>
+      <x:c r="H166"/>
+      <x:c r="I166"/>
     </x:row>
     <x:row r="167" ht="23" customHeight="1">
       <x:c r="A167" s="40"/>
@@ -2092,6 +2484,8 @@
       <x:c r="E167" s="46"/>
       <x:c r="F167" s="40"/>
       <x:c r="G167" s="50"/>
+      <x:c r="H167"/>
+      <x:c r="I167"/>
     </x:row>
     <x:row r="168" ht="23" customHeight="1">
       <x:c r="A168" s="40"/>
@@ -2101,6 +2495,8 @@
       <x:c r="E168" s="46"/>
       <x:c r="F168" s="40"/>
       <x:c r="G168" s="50"/>
+      <x:c r="H168"/>
+      <x:c r="I168"/>
     </x:row>
     <x:row r="169" ht="23" customHeight="1">
       <x:c r="A169" s="40"/>
@@ -2110,6 +2506,8 @@
       <x:c r="E169" s="46"/>
       <x:c r="F169" s="40"/>
       <x:c r="G169" s="50"/>
+      <x:c r="H169"/>
+      <x:c r="I169"/>
     </x:row>
     <x:row r="170" ht="23" customHeight="1">
       <x:c r="A170" s="40"/>
@@ -2119,6 +2517,8 @@
       <x:c r="E170" s="46"/>
       <x:c r="F170" s="40"/>
       <x:c r="G170" s="50"/>
+      <x:c r="H170"/>
+      <x:c r="I170"/>
     </x:row>
     <x:row r="171" ht="23" customHeight="1">
       <x:c r="A171" s="40"/>
@@ -2128,6 +2528,8 @@
       <x:c r="E171" s="46"/>
       <x:c r="F171" s="40"/>
       <x:c r="G171" s="50"/>
+      <x:c r="H171"/>
+      <x:c r="I171"/>
     </x:row>
     <x:row r="172" ht="23" customHeight="1">
       <x:c r="A172" s="40"/>
@@ -2137,6 +2539,8 @@
       <x:c r="E172" s="46"/>
       <x:c r="F172" s="40"/>
       <x:c r="G172" s="50"/>
+      <x:c r="H172"/>
+      <x:c r="I172"/>
     </x:row>
     <x:row r="173" ht="23" customHeight="1">
       <x:c r="A173" s="40"/>
@@ -2146,6 +2550,8 @@
       <x:c r="E173" s="46"/>
       <x:c r="F173" s="40"/>
       <x:c r="G173" s="50"/>
+      <x:c r="H173"/>
+      <x:c r="I173"/>
     </x:row>
     <x:row r="174" ht="23" customHeight="1">
       <x:c r="A174" s="40"/>
@@ -2155,6 +2561,8 @@
       <x:c r="E174" s="46"/>
       <x:c r="F174" s="40"/>
       <x:c r="G174" s="50"/>
+      <x:c r="H174"/>
+      <x:c r="I174"/>
     </x:row>
     <x:row r="175" ht="23" customHeight="1">
       <x:c r="A175" s="40"/>
@@ -2164,6 +2572,8 @@
       <x:c r="E175" s="46"/>
       <x:c r="F175" s="40"/>
       <x:c r="G175" s="50"/>
+      <x:c r="H175"/>
+      <x:c r="I175"/>
     </x:row>
     <x:row r="176" ht="23" customHeight="1">
       <x:c r="A176" s="40"/>
@@ -2173,6 +2583,8 @@
       <x:c r="E176" s="46"/>
       <x:c r="F176" s="40"/>
       <x:c r="G176" s="50"/>
+      <x:c r="H176"/>
+      <x:c r="I176"/>
     </x:row>
     <x:row r="177" ht="23" customHeight="1">
       <x:c r="A177" s="40"/>
@@ -2182,6 +2594,8 @@
       <x:c r="E177" s="46"/>
       <x:c r="F177" s="40"/>
       <x:c r="G177" s="50"/>
+      <x:c r="H177"/>
+      <x:c r="I177"/>
     </x:row>
     <x:row r="178" ht="23" customHeight="1">
       <x:c r="A178" s="40"/>
@@ -2191,6 +2605,8 @@
       <x:c r="E178" s="46"/>
       <x:c r="F178" s="40"/>
       <x:c r="G178" s="50"/>
+      <x:c r="H178"/>
+      <x:c r="I178"/>
     </x:row>
     <x:row r="179" ht="23" customHeight="1">
       <x:c r="A179" s="40"/>
@@ -2200,6 +2616,8 @@
       <x:c r="E179" s="46"/>
       <x:c r="F179" s="40"/>
       <x:c r="G179" s="50"/>
+      <x:c r="H179"/>
+      <x:c r="I179"/>
     </x:row>
     <x:row r="180" ht="23" customHeight="1">
       <x:c r="A180" s="40"/>
@@ -2209,6 +2627,8 @@
       <x:c r="E180" s="46"/>
       <x:c r="F180" s="40"/>
       <x:c r="G180" s="50"/>
+      <x:c r="H180"/>
+      <x:c r="I180"/>
     </x:row>
     <x:row r="181" ht="23" customHeight="1">
       <x:c r="A181" s="40"/>
@@ -2218,6 +2638,8 @@
       <x:c r="E181" s="46"/>
       <x:c r="F181" s="40"/>
       <x:c r="G181" s="50"/>
+      <x:c r="H181"/>
+      <x:c r="I181"/>
     </x:row>
     <x:row r="182" ht="23" customHeight="1">
       <x:c r="A182" s="40"/>
@@ -2227,6 +2649,8 @@
       <x:c r="E182" s="46"/>
       <x:c r="F182" s="40"/>
       <x:c r="G182" s="50"/>
+      <x:c r="H182"/>
+      <x:c r="I182"/>
     </x:row>
     <x:row r="183" ht="23" customHeight="1">
       <x:c r="A183" s="40"/>
@@ -2236,6 +2660,8 @@
       <x:c r="E183" s="46"/>
       <x:c r="F183" s="40"/>
       <x:c r="G183" s="50"/>
+      <x:c r="H183"/>
+      <x:c r="I183"/>
     </x:row>
     <x:row r="184" ht="23" customHeight="1">
       <x:c r="A184" s="40"/>
@@ -2245,6 +2671,8 @@
       <x:c r="E184" s="46"/>
       <x:c r="F184" s="40"/>
       <x:c r="G184" s="50"/>
+      <x:c r="H184"/>
+      <x:c r="I184"/>
     </x:row>
     <x:row r="185" ht="23" customHeight="1">
       <x:c r="A185" s="40"/>
@@ -2254,6 +2682,8 @@
       <x:c r="E185" s="46"/>
       <x:c r="F185" s="40"/>
       <x:c r="G185" s="50"/>
+      <x:c r="H185"/>
+      <x:c r="I185"/>
     </x:row>
     <x:row r="186" ht="23" customHeight="1">
       <x:c r="A186" s="40"/>
@@ -2263,6 +2693,8 @@
       <x:c r="E186" s="46"/>
       <x:c r="F186" s="40"/>
       <x:c r="G186" s="50"/>
+      <x:c r="H186"/>
+      <x:c r="I186"/>
     </x:row>
     <x:row r="187" ht="23" customHeight="1">
       <x:c r="A187" s="40"/>
@@ -2272,6 +2704,8 @@
       <x:c r="E187" s="46"/>
       <x:c r="F187" s="40"/>
       <x:c r="G187" s="50"/>
+      <x:c r="H187"/>
+      <x:c r="I187"/>
     </x:row>
     <x:row r="188" ht="23" customHeight="1">
       <x:c r="A188" s="40"/>
@@ -2281,6 +2715,8 @@
       <x:c r="E188" s="46"/>
       <x:c r="F188" s="40"/>
       <x:c r="G188" s="50"/>
+      <x:c r="H188"/>
+      <x:c r="I188"/>
     </x:row>
     <x:row r="189" ht="23" customHeight="1">
       <x:c r="A189" s="40"/>
@@ -2290,6 +2726,8 @@
       <x:c r="E189" s="46"/>
       <x:c r="F189" s="40"/>
       <x:c r="G189" s="50"/>
+      <x:c r="H189"/>
+      <x:c r="I189"/>
     </x:row>
     <x:row r="190" ht="23" customHeight="1">
       <x:c r="A190" s="40"/>
@@ -2299,6 +2737,8 @@
       <x:c r="E190" s="46"/>
       <x:c r="F190" s="40"/>
       <x:c r="G190" s="50"/>
+      <x:c r="H190"/>
+      <x:c r="I190"/>
     </x:row>
     <x:row r="191" ht="23" customHeight="1">
       <x:c r="A191" s="40"/>
@@ -2308,6 +2748,8 @@
       <x:c r="E191" s="46"/>
       <x:c r="F191" s="40"/>
       <x:c r="G191" s="50"/>
+      <x:c r="H191"/>
+      <x:c r="I191"/>
     </x:row>
     <x:row r="192" ht="23" customHeight="1">
       <x:c r="A192" s="40"/>
@@ -2317,6 +2759,8 @@
       <x:c r="E192" s="46"/>
       <x:c r="F192" s="40"/>
       <x:c r="G192" s="50"/>
+      <x:c r="H192"/>
+      <x:c r="I192"/>
     </x:row>
     <x:row r="193" ht="23" customHeight="1">
       <x:c r="A193" s="40"/>
@@ -2326,6 +2770,8 @@
       <x:c r="E193" s="46"/>
       <x:c r="F193" s="40"/>
       <x:c r="G193" s="50"/>
+      <x:c r="H193"/>
+      <x:c r="I193"/>
     </x:row>
     <x:row r="194" ht="23" customHeight="1">
       <x:c r="A194" s="40"/>
@@ -2335,6 +2781,8 @@
       <x:c r="E194" s="46"/>
       <x:c r="F194" s="40"/>
       <x:c r="G194" s="50"/>
+      <x:c r="H194"/>
+      <x:c r="I194"/>
     </x:row>
     <x:row r="195" ht="23" customHeight="1">
       <x:c r="A195" s="40"/>
@@ -2344,6 +2792,8 @@
       <x:c r="E195" s="46"/>
       <x:c r="F195" s="40"/>
       <x:c r="G195" s="50"/>
+      <x:c r="H195"/>
+      <x:c r="I195"/>
     </x:row>
     <x:row r="196" ht="23" customHeight="1">
       <x:c r="A196" s="40"/>
@@ -2353,6 +2803,8 @@
       <x:c r="E196" s="46"/>
       <x:c r="F196" s="40"/>
       <x:c r="G196" s="50"/>
+      <x:c r="H196"/>
+      <x:c r="I196"/>
     </x:row>
     <x:row r="197" ht="23" customHeight="1">
       <x:c r="A197" s="40"/>
@@ -2362,6 +2814,8 @@
       <x:c r="E197" s="46"/>
       <x:c r="F197" s="40"/>
       <x:c r="G197" s="50"/>
+      <x:c r="H197"/>
+      <x:c r="I197"/>
     </x:row>
     <x:row r="198" ht="23" customHeight="1">
       <x:c r="A198" s="40"/>
@@ -2371,6 +2825,8 @@
       <x:c r="E198" s="46"/>
       <x:c r="F198" s="40"/>
       <x:c r="G198" s="50"/>
+      <x:c r="H198"/>
+      <x:c r="I198"/>
     </x:row>
     <x:row r="199" ht="23" customHeight="1">
       <x:c r="A199" s="40"/>
@@ -2380,6 +2836,8 @@
       <x:c r="E199" s="46"/>
       <x:c r="F199" s="40"/>
       <x:c r="G199" s="50"/>
+      <x:c r="H199"/>
+      <x:c r="I199"/>
     </x:row>
     <x:row r="200" ht="23" customHeight="1">
       <x:c r="A200" s="40"/>
@@ -2389,6 +2847,8 @@
       <x:c r="E200" s="46"/>
       <x:c r="F200" s="40"/>
       <x:c r="G200" s="50"/>
+      <x:c r="H200"/>
+      <x:c r="I200"/>
     </x:row>
     <x:row r="201" ht="23" customHeight="1">
       <x:c r="A201" s="40"/>
@@ -2398,6 +2858,8 @@
       <x:c r="E201" s="46"/>
       <x:c r="F201" s="40"/>
       <x:c r="G201" s="50"/>
+      <x:c r="H201"/>
+      <x:c r="I201"/>
     </x:row>
     <x:row r="202" ht="23" customHeight="1">
       <x:c r="A202" s="40"/>
@@ -2407,6 +2869,8 @@
       <x:c r="E202" s="46"/>
       <x:c r="F202" s="40"/>
       <x:c r="G202" s="50"/>
+      <x:c r="H202"/>
+      <x:c r="I202"/>
     </x:row>
     <x:row r="203" ht="23" customHeight="1">
       <x:c r="A203" s="40"/>
@@ -2416,6 +2880,8 @@
       <x:c r="E203" s="46"/>
       <x:c r="F203" s="40"/>
       <x:c r="G203" s="50"/>
+      <x:c r="H203"/>
+      <x:c r="I203"/>
     </x:row>
     <x:row r="204" ht="23" customHeight="1">
       <x:c r="A204" s="40"/>
@@ -2425,6 +2891,8 @@
       <x:c r="E204" s="46"/>
       <x:c r="F204" s="40"/>
       <x:c r="G204" s="50"/>
+      <x:c r="H204"/>
+      <x:c r="I204"/>
     </x:row>
     <x:row r="205" ht="23" customHeight="1">
       <x:c r="A205" s="40"/>
@@ -2434,6 +2902,8 @@
       <x:c r="E205" s="46"/>
       <x:c r="F205" s="40"/>
       <x:c r="G205" s="50"/>
+      <x:c r="H205"/>
+      <x:c r="I205"/>
     </x:row>
     <x:row r="206" ht="23" customHeight="1">
       <x:c r="A206" s="40"/>

--- a/P360_Config_Template.xlsx
+++ b/P360_Config_Template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rbe720aead74c4a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="2" r:id="R4431bdc37d2f4b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R1696afc9b484486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apps" sheetId="2" r:id="R5b57bc710285412a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,14 +45,8 @@
       <x:color rgb="FF2A1D12"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF8A552A"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -79,59 +73,65 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2A1D12"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF1E5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2A1D12"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF1E5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2A1D12"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF1E5"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="16">
     <x:border/>
     <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="70">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -244,44 +244,6 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -332,9 +294,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -525,22 +487,6 @@
         <x:v>Upload this workbook from the dashboard. Manually saved server rows are combined with uploaded Excel rows.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="34" customHeight="1">
-      <x:c r="A12" s="61" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Optional: add comma-separated Affise Offer IDs for each app to enable the app-level Affise vs AppsFlyer overall-click comparison. Repeat the same offer IDs on that app's PID rows.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="69" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="19" t="str">
-        <x:v>Optional: enter the exact, case-sensitive AppsFlyer Billable Event Name for each App + PID + PRT row. P360 counts only accepted raw in-app events; blocked-event reports and blocked-event postbacks are excluded.</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -560,8 +506,6 @@
     <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -586,12 +530,6 @@
       <x:c r="G1" s="35" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="H1" s="60" t="str">
-        <x:v>Affise Offer IDs</x:v>
-      </x:c>
-      <x:c r="I1" s="66" t="str">
-        <x:v>Billable Event Name</x:v>
-      </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="40" t="str">
@@ -615,8 +553,6 @@
       <x:c r="G2" s="50" t="str">
         <x:v>Example row</x:v>
       </x:c>
-      <x:c r="H2" t="str"/>
-      <x:c r="I2" t="str"/>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="40" t="str">
@@ -640,8 +576,6 @@
       <x:c r="G3" s="50" t="str">
         <x:v>Separate PID row</x:v>
       </x:c>
-      <x:c r="H3" t="str"/>
-      <x:c r="I3" t="str"/>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="40" t="str">
@@ -665,8 +599,6 @@
       <x:c r="G4" s="50" t="str">
         <x:v>Philippines timezone</x:v>
       </x:c>
-      <x:c r="H4" t="str"/>
-      <x:c r="I4" t="str"/>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="40" t="str">
@@ -690,8 +622,6 @@
       <x:c r="G5" s="50" t="str">
         <x:v>Indonesia timezone</x:v>
       </x:c>
-      <x:c r="H5" t="str"/>
-      <x:c r="I5" t="str"/>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="40" t="str">
@@ -705,8 +635,6 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G6" s="50" t="str"/>
-      <x:c r="H6" t="str"/>
-      <x:c r="I6" t="str"/>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="40" t="str">
@@ -720,8 +648,6 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G7" s="50" t="str"/>
-      <x:c r="H7" t="str"/>
-      <x:c r="I7" t="str"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="40" t="str">
@@ -735,8 +661,6 @@
         <x:v>UTC</x:v>
       </x:c>
       <x:c r="G8" s="50" t="str"/>
-      <x:c r="H8" t="str"/>
-      <x:c r="I8" t="str"/>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="40"/>
@@ -746,8 +670,6 @@
       <x:c r="E9" s="46"/>
       <x:c r="F9" s="40"/>
       <x:c r="G9" s="50"/>
-      <x:c r="H9"/>
-      <x:c r="I9"/>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="40"/>
@@ -757,8 +679,6 @@
       <x:c r="E10" s="46"/>
       <x:c r="F10" s="40"/>
       <x:c r="G10" s="50"/>
-      <x:c r="H10"/>
-      <x:c r="I10"/>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="40"/>
@@ -768,8 +688,6 @@
       <x:c r="E11" s="46"/>
       <x:c r="F11" s="40"/>
       <x:c r="G11" s="50"/>
-      <x:c r="H11"/>
-      <x:c r="I11"/>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="40"/>
@@ -779,8 +697,6 @@
       <x:c r="E12" s="46"/>
       <x:c r="F12" s="40"/>
       <x:c r="G12" s="50"/>
-      <x:c r="H12"/>
-      <x:c r="I12"/>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="40"/>
@@ -790,8 +706,6 @@
       <x:c r="E13" s="46"/>
       <x:c r="F13" s="40"/>
       <x:c r="G13" s="50"/>
-      <x:c r="H13"/>
-      <x:c r="I13"/>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="40"/>
@@ -801,8 +715,6 @@
       <x:c r="E14" s="46"/>
       <x:c r="F14" s="40"/>
       <x:c r="G14" s="50"/>
-      <x:c r="H14"/>
-      <x:c r="I14"/>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="40"/>
@@ -812,8 +724,6 @@
       <x:c r="E15" s="46"/>
       <x:c r="F15" s="40"/>
       <x:c r="G15" s="50"/>
-      <x:c r="H15"/>
-      <x:c r="I15"/>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="40"/>
@@ -823,8 +733,6 @@
       <x:c r="E16" s="46"/>
       <x:c r="F16" s="40"/>
       <x:c r="G16" s="50"/>
-      <x:c r="H16"/>
-      <x:c r="I16"/>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="40"/>
@@ -834,8 +742,6 @@
       <x:c r="E17" s="46"/>
       <x:c r="F17" s="40"/>
       <x:c r="G17" s="50"/>
-      <x:c r="H17"/>
-      <x:c r="I17"/>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
       <x:c r="A18" s="40"/>
@@ -845,8 +751,6 @@
       <x:c r="E18" s="46"/>
       <x:c r="F18" s="40"/>
       <x:c r="G18" s="50"/>
-      <x:c r="H18"/>
-      <x:c r="I18"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="40"/>
@@ -856,8 +760,6 @@
       <x:c r="E19" s="46"/>
       <x:c r="F19" s="40"/>
       <x:c r="G19" s="50"/>
-      <x:c r="H19"/>
-      <x:c r="I19"/>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="40"/>
@@ -867,8 +769,6 @@
       <x:c r="E20" s="46"/>
       <x:c r="F20" s="40"/>
       <x:c r="G20" s="50"/>
-      <x:c r="H20"/>
-      <x:c r="I20"/>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="40"/>
@@ -878,8 +778,6 @@
       <x:c r="E21" s="46"/>
       <x:c r="F21" s="40"/>
       <x:c r="G21" s="50"/>
-      <x:c r="H21"/>
-      <x:c r="I21"/>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="40"/>
@@ -889,8 +787,6 @@
       <x:c r="E22" s="46"/>
       <x:c r="F22" s="40"/>
       <x:c r="G22" s="50"/>
-      <x:c r="H22"/>
-      <x:c r="I22"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="40"/>
@@ -900,8 +796,6 @@
       <x:c r="E23" s="46"/>
       <x:c r="F23" s="40"/>
       <x:c r="G23" s="50"/>
-      <x:c r="H23"/>
-      <x:c r="I23"/>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
       <x:c r="A24" s="40"/>
@@ -911,8 +805,6 @@
       <x:c r="E24" s="46"/>
       <x:c r="F24" s="40"/>
       <x:c r="G24" s="50"/>
-      <x:c r="H24"/>
-      <x:c r="I24"/>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
       <x:c r="A25" s="40"/>
@@ -922,8 +814,6 @@
       <x:c r="E25" s="46"/>
       <x:c r="F25" s="40"/>
       <x:c r="G25" s="50"/>
-      <x:c r="H25"/>
-      <x:c r="I25"/>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
       <x:c r="A26" s="40"/>
@@ -933,8 +823,6 @@
       <x:c r="E26" s="46"/>
       <x:c r="F26" s="40"/>
       <x:c r="G26" s="50"/>
-      <x:c r="H26"/>
-      <x:c r="I26"/>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="40"/>
@@ -944,8 +832,6 @@
       <x:c r="E27" s="46"/>
       <x:c r="F27" s="40"/>
       <x:c r="G27" s="50"/>
-      <x:c r="H27"/>
-      <x:c r="I27"/>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
       <x:c r="A28" s="40"/>
@@ -955,8 +841,6 @@
       <x:c r="E28" s="46"/>
       <x:c r="F28" s="40"/>
       <x:c r="G28" s="50"/>
-      <x:c r="H28"/>
-      <x:c r="I28"/>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
       <x:c r="A29" s="40"/>
@@ -966,8 +850,6 @@
       <x:c r="E29" s="46"/>
       <x:c r="F29" s="40"/>
       <x:c r="G29" s="50"/>
-      <x:c r="H29"/>
-      <x:c r="I29"/>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
       <x:c r="A30" s="40"/>
@@ -977,8 +859,6 @@
       <x:c r="E30" s="46"/>
       <x:c r="F30" s="40"/>
       <x:c r="G30" s="50"/>
-      <x:c r="H30"/>
-      <x:c r="I30"/>
     </x:row>
     <x:row r="31" ht="23" customHeight="1">
       <x:c r="A31" s="40"/>
@@ -988,8 +868,6 @@
       <x:c r="E31" s="46"/>
       <x:c r="F31" s="40"/>
       <x:c r="G31" s="50"/>
-      <x:c r="H31"/>
-      <x:c r="I31"/>
     </x:row>
     <x:row r="32" ht="23" customHeight="1">
       <x:c r="A32" s="40"/>
@@ -999,8 +877,6 @@
       <x:c r="E32" s="46"/>
       <x:c r="F32" s="40"/>
       <x:c r="G32" s="50"/>
-      <x:c r="H32"/>
-      <x:c r="I32"/>
     </x:row>
     <x:row r="33" ht="23" customHeight="1">
       <x:c r="A33" s="40"/>
@@ -1010,8 +886,6 @@
       <x:c r="E33" s="46"/>
       <x:c r="F33" s="40"/>
       <x:c r="G33" s="50"/>
-      <x:c r="H33"/>
-      <x:c r="I33"/>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
       <x:c r="A34" s="40"/>
@@ -1021,8 +895,6 @@
       <x:c r="E34" s="46"/>
       <x:c r="F34" s="40"/>
       <x:c r="G34" s="50"/>
-      <x:c r="H34"/>
-      <x:c r="I34"/>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
       <x:c r="A35" s="40"/>
@@ -1032,8 +904,6 @@
       <x:c r="E35" s="46"/>
       <x:c r="F35" s="40"/>
       <x:c r="G35" s="50"/>
-      <x:c r="H35"/>
-      <x:c r="I35"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="40"/>
@@ -1043,8 +913,6 @@
       <x:c r="E36" s="46"/>
       <x:c r="F36" s="40"/>
       <x:c r="G36" s="50"/>
-      <x:c r="H36"/>
-      <x:c r="I36"/>
     </x:row>
     <x:row r="37" ht="23" customHeight="1">
       <x:c r="A37" s="40"/>
@@ -1054,8 +922,6 @@
       <x:c r="E37" s="46"/>
       <x:c r="F37" s="40"/>
       <x:c r="G37" s="50"/>
-      <x:c r="H37"/>
-      <x:c r="I37"/>
     </x:row>
     <x:row r="38" ht="23" customHeight="1">
       <x:c r="A38" s="40"/>
@@ -1065,8 +931,6 @@
       <x:c r="E38" s="46"/>
       <x:c r="F38" s="40"/>
       <x:c r="G38" s="50"/>
-      <x:c r="H38"/>
-      <x:c r="I38"/>
     </x:row>
     <x:row r="39" ht="23" customHeight="1">
       <x:c r="A39" s="40"/>
@@ -1076,8 +940,6 @@
       <x:c r="E39" s="46"/>
       <x:c r="F39" s="40"/>
       <x:c r="G39" s="50"/>
-      <x:c r="H39"/>
-      <x:c r="I39"/>
     </x:row>
     <x:row r="40" ht="23" customHeight="1">
       <x:c r="A40" s="40"/>
@@ -1087,8 +949,6 @@
       <x:c r="E40" s="46"/>
       <x:c r="F40" s="40"/>
       <x:c r="G40" s="50"/>
-      <x:c r="H40"/>
-      <x:c r="I40"/>
     </x:row>
     <x:row r="41" ht="23" customHeight="1">
       <x:c r="A41" s="40"/>
@@ -1098,8 +958,6 @@
       <x:c r="E41" s="46"/>
       <x:c r="F41" s="40"/>
       <x:c r="G41" s="50"/>
-      <x:c r="H41"/>
-      <x:c r="I41"/>
     </x:row>
     <x:row r="42" ht="23" customHeight="1">
       <x:c r="A42" s="40"/>
@@ -1109,8 +967,6 @@
       <x:c r="E42" s="46"/>
       <x:c r="F42" s="40"/>
       <x:c r="G42" s="50"/>
-      <x:c r="H42"/>
-      <x:c r="I42"/>
     </x:row>
     <x:row r="43" ht="23" customHeight="1">
       <x:c r="A43" s="40"/>
@@ -1120,8 +976,6 @@
       <x:c r="E43" s="46"/>
       <x:c r="F43" s="40"/>
       <x:c r="G43" s="50"/>
-      <x:c r="H43"/>
-      <x:c r="I43"/>
     </x:row>
     <x:row r="44" ht="23" customHeight="1">
       <x:c r="A44" s="40"/>
@@ -1131,8 +985,6 @@
       <x:c r="E44" s="46"/>
       <x:c r="F44" s="40"/>
       <x:c r="G44" s="50"/>
-      <x:c r="H44"/>
-      <x:c r="I44"/>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="40"/>
@@ -1142,8 +994,6 @@
       <x:c r="E45" s="46"/>
       <x:c r="F45" s="40"/>
       <x:c r="G45" s="50"/>
-      <x:c r="H45"/>
-      <x:c r="I45"/>
     </x:row>
     <x:row r="46" ht="23" customHeight="1">
       <x:c r="A46" s="40"/>
@@ -1153,8 +1003,6 @@
       <x:c r="E46" s="46"/>
       <x:c r="F46" s="40"/>
       <x:c r="G46" s="50"/>
-      <x:c r="H46"/>
-      <x:c r="I46"/>
     </x:row>
     <x:row r="47" ht="23" customHeight="1">
       <x:c r="A47" s="40"/>
@@ -1164,8 +1012,6 @@
       <x:c r="E47" s="46"/>
       <x:c r="F47" s="40"/>
       <x:c r="G47" s="50"/>
-      <x:c r="H47"/>
-      <x:c r="I47"/>
     </x:row>
     <x:row r="48" ht="23" customHeight="1">
       <x:c r="A48" s="40"/>
@@ -1175,8 +1021,6 @@
       <x:c r="E48" s="46"/>
       <x:c r="F48" s="40"/>
       <x:c r="G48" s="50"/>
-      <x:c r="H48"/>
-      <x:c r="I48"/>
     </x:row>
     <x:row r="49" ht="23" customHeight="1">
       <x:c r="A49" s="40"/>
@@ -1186,8 +1030,6 @@
       <x:c r="E49" s="46"/>
       <x:c r="F49" s="40"/>
       <x:c r="G49" s="50"/>
-      <x:c r="H49"/>
-      <x:c r="I49"/>
     </x:row>
     <x:row r="50" ht="23" customHeight="1">
       <x:c r="A50" s="40"/>
@@ -1197,8 +1039,6 @@
       <x:c r="E50" s="46"/>
       <x:c r="F50" s="40"/>
       <x:c r="G50" s="50"/>
-      <x:c r="H50"/>
-      <x:c r="I50"/>
     </x:row>
     <x:row r="51" ht="23" customHeight="1">
       <x:c r="A51" s="40"/>
@@ -1208,8 +1048,6 @@
       <x:c r="E51" s="46"/>
       <x:c r="F51" s="40"/>
       <x:c r="G51" s="50"/>
-      <x:c r="H51"/>
-      <x:c r="I51"/>
     </x:row>
     <x:row r="52" ht="23" customHeight="1">
       <x:c r="A52" s="40"/>
@@ -1219,8 +1057,6 @@
       <x:c r="E52" s="46"/>
       <x:c r="F52" s="40"/>
       <x:c r="G52" s="50"/>
-      <x:c r="H52"/>
-      <x:c r="I52"/>
     </x:row>
     <x:row r="53" ht="23" customHeight="1">
       <x:c r="A53" s="40"/>
@@ -1230,8 +1066,6 @@
       <x:c r="E53" s="46"/>
       <x:c r="F53" s="40"/>
       <x:c r="G53" s="50"/>
-      <x:c r="H53"/>
-      <x:c r="I53"/>
     </x:row>
     <x:row r="54" ht="23" customHeight="1">
       <x:c r="A54" s="40"/>
@@ -1241,8 +1075,6 @@
       <x:c r="E54" s="46"/>
       <x:c r="F54" s="40"/>
       <x:c r="G54" s="50"/>
-      <x:c r="H54"/>
-      <x:c r="I54"/>
     </x:row>
     <x:row r="55" ht="23" customHeight="1">
       <x:c r="A55" s="40"/>
@@ -1252,8 +1084,6 @@
       <x:c r="E55" s="46"/>
       <x:c r="F55" s="40"/>
       <x:c r="G55" s="50"/>
-      <x:c r="H55"/>
-      <x:c r="I55"/>
     </x:row>
     <x:row r="56" ht="23" customHeight="1">
       <x:c r="A56" s="40"/>
@@ -1263,8 +1093,6 @@
       <x:c r="E56" s="46"/>
       <x:c r="F56" s="40"/>
       <x:c r="G56" s="50"/>
-      <x:c r="H56"/>
-      <x:c r="I56"/>
     </x:row>
     <x:row r="57" ht="23" customHeight="1">
       <x:c r="A57" s="40"/>
@@ -1274,8 +1102,6 @@
       <x:c r="E57" s="46"/>
       <x:c r="F57" s="40"/>
       <x:c r="G57" s="50"/>
-      <x:c r="H57"/>
-      <x:c r="I57"/>
     </x:row>
     <x:row r="58" ht="23" customHeight="1">
       <x:c r="A58" s="40"/>
@@ -1285,8 +1111,6 @@
       <x:c r="E58" s="46"/>
       <x:c r="F58" s="40"/>
       <x:c r="G58" s="50"/>
-      <x:c r="H58"/>
-      <x:c r="I58"/>
     </x:row>
     <x:row r="59" ht="23" customHeight="1">
       <x:c r="A59" s="40"/>
@@ -1296,8 +1120,6 @@
       <x:c r="E59" s="46"/>
       <x:c r="F59" s="40"/>
       <x:c r="G59" s="50"/>
-      <x:c r="H59"/>
-      <x:c r="I59"/>
     </x:row>
     <x:row r="60" ht="23" customHeight="1">
       <x:c r="A60" s="40"/>
@@ -1307,8 +1129,6 @@
       <x:c r="E60" s="46"/>
       <x:c r="F60" s="40"/>
       <x:c r="G60" s="50"/>
-      <x:c r="H60"/>
-      <x:c r="I60"/>
     </x:row>
     <x:row r="61" ht="23" customHeight="1">
       <x:c r="A61" s="40"/>
@@ -1318,8 +1138,6 @@
       <x:c r="E61" s="46"/>
       <x:c r="F61" s="40"/>
       <x:c r="G61" s="50"/>
-      <x:c r="H61"/>
-      <x:c r="I61"/>
     </x:row>
     <x:row r="62" ht="23" customHeight="1">
       <x:c r="A62" s="40"/>
@@ -1329,8 +1147,6 @@
       <x:c r="E62" s="46"/>
       <x:c r="F62" s="40"/>
       <x:c r="G62" s="50"/>
-      <x:c r="H62"/>
-      <x:c r="I62"/>
     </x:row>
     <x:row r="63" ht="23" customHeight="1">
       <x:c r="A63" s="40"/>
@@ -1340,8 +1156,6 @@
       <x:c r="E63" s="46"/>
       <x:c r="F63" s="40"/>
       <x:c r="G63" s="50"/>
-      <x:c r="H63"/>
-      <x:c r="I63"/>
     </x:row>
     <x:row r="64" ht="23" customHeight="1">
       <x:c r="A64" s="40"/>
@@ -1351,8 +1165,6 @@
       <x:c r="E64" s="46"/>
       <x:c r="F64" s="40"/>
       <x:c r="G64" s="50"/>
-      <x:c r="H64"/>
-      <x:c r="I64"/>
     </x:row>
     <x:row r="65" ht="23" customHeight="1">
       <x:c r="A65" s="40"/>
@@ -1362,8 +1174,6 @@
       <x:c r="E65" s="46"/>
       <x:c r="F65" s="40"/>
       <x:c r="G65" s="50"/>
-      <x:c r="H65"/>
-      <x:c r="I65"/>
     </x:row>
     <x:row r="66" ht="23" customHeight="1">
       <x:c r="A66" s="40"/>
@@ -1373,8 +1183,6 @@
       <x:c r="E66" s="46"/>
       <x:c r="F66" s="40"/>
       <x:c r="G66" s="50"/>
-      <x:c r="H66"/>
-      <x:c r="I66"/>
     </x:row>
     <x:row r="67" ht="23" customHeight="1">
       <x:c r="A67" s="40"/>
@@ -1384,8 +1192,6 @@
       <x:c r="E67" s="46"/>
       <x:c r="F67" s="40"/>
       <x:c r="G67" s="50"/>
-      <x:c r="H67"/>
-      <x:c r="I67"/>
     </x:row>
     <x:row r="68" ht="23" customHeight="1">
       <x:c r="A68" s="40"/>
@@ -1395,8 +1201,6 @@
       <x:c r="E68" s="46"/>
       <x:c r="F68" s="40"/>
       <x:c r="G68" s="50"/>
-      <x:c r="H68"/>
-      <x:c r="I68"/>
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="40"/>
@@ -1406,8 +1210,6 @@
       <x:c r="E69" s="46"/>
       <x:c r="F69" s="40"/>
       <x:c r="G69" s="50"/>
-      <x:c r="H69"/>
-      <x:c r="I69"/>
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="40"/>
@@ -1417,8 +1219,6 @@
       <x:c r="E70" s="46"/>
       <x:c r="F70" s="40"/>
       <x:c r="G70" s="50"/>
-      <x:c r="H70"/>
-      <x:c r="I70"/>
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="40"/>
@@ -1428,8 +1228,6 @@
       <x:c r="E71" s="46"/>
       <x:c r="F71" s="40"/>
       <x:c r="G71" s="50"/>
-      <x:c r="H71"/>
-      <x:c r="I71"/>
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="40"/>
@@ -1439,8 +1237,6 @@
       <x:c r="E72" s="46"/>
       <x:c r="F72" s="40"/>
       <x:c r="G72" s="50"/>
-      <x:c r="H72"/>
-      <x:c r="I72"/>
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="40"/>
@@ -1450,8 +1246,6 @@
       <x:c r="E73" s="46"/>
       <x:c r="F73" s="40"/>
       <x:c r="G73" s="50"/>
-      <x:c r="H73"/>
-      <x:c r="I73"/>
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="40"/>
@@ -1461,8 +1255,6 @@
       <x:c r="E74" s="46"/>
       <x:c r="F74" s="40"/>
       <x:c r="G74" s="50"/>
-      <x:c r="H74"/>
-      <x:c r="I74"/>
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="40"/>
@@ -1472,8 +1264,6 @@
       <x:c r="E75" s="46"/>
       <x:c r="F75" s="40"/>
       <x:c r="G75" s="50"/>
-      <x:c r="H75"/>
-      <x:c r="I75"/>
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="40"/>
@@ -1483,8 +1273,6 @@
       <x:c r="E76" s="46"/>
       <x:c r="F76" s="40"/>
       <x:c r="G76" s="50"/>
-      <x:c r="H76"/>
-      <x:c r="I76"/>
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="40"/>
@@ -1494,8 +1282,6 @@
       <x:c r="E77" s="46"/>
       <x:c r="F77" s="40"/>
       <x:c r="G77" s="50"/>
-      <x:c r="H77"/>
-      <x:c r="I77"/>
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="40"/>
@@ -1505,8 +1291,6 @@
       <x:c r="E78" s="46"/>
       <x:c r="F78" s="40"/>
       <x:c r="G78" s="50"/>
-      <x:c r="H78"/>
-      <x:c r="I78"/>
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="40"/>
@@ -1516,8 +1300,6 @@
       <x:c r="E79" s="46"/>
       <x:c r="F79" s="40"/>
       <x:c r="G79" s="50"/>
-      <x:c r="H79"/>
-      <x:c r="I79"/>
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="40"/>
@@ -1527,8 +1309,6 @@
       <x:c r="E80" s="46"/>
       <x:c r="F80" s="40"/>
       <x:c r="G80" s="50"/>
-      <x:c r="H80"/>
-      <x:c r="I80"/>
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="40"/>
@@ -1538,8 +1318,6 @@
       <x:c r="E81" s="46"/>
       <x:c r="F81" s="40"/>
       <x:c r="G81" s="50"/>
-      <x:c r="H81"/>
-      <x:c r="I81"/>
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="40"/>
@@ -1549,8 +1327,6 @@
       <x:c r="E82" s="46"/>
       <x:c r="F82" s="40"/>
       <x:c r="G82" s="50"/>
-      <x:c r="H82"/>
-      <x:c r="I82"/>
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="40"/>
@@ -1560,8 +1336,6 @@
       <x:c r="E83" s="46"/>
       <x:c r="F83" s="40"/>
       <x:c r="G83" s="50"/>
-      <x:c r="H83"/>
-      <x:c r="I83"/>
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="40"/>
@@ -1571,8 +1345,6 @@
       <x:c r="E84" s="46"/>
       <x:c r="F84" s="40"/>
       <x:c r="G84" s="50"/>
-      <x:c r="H84"/>
-      <x:c r="I84"/>
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="40"/>
@@ -1582,8 +1354,6 @@
       <x:c r="E85" s="46"/>
       <x:c r="F85" s="40"/>
       <x:c r="G85" s="50"/>
-      <x:c r="H85"/>
-      <x:c r="I85"/>
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="40"/>
@@ -1593,8 +1363,6 @@
       <x:c r="E86" s="46"/>
       <x:c r="F86" s="40"/>
       <x:c r="G86" s="50"/>
-      <x:c r="H86"/>
-      <x:c r="I86"/>
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="40"/>
@@ -1604,8 +1372,6 @@
       <x:c r="E87" s="46"/>
       <x:c r="F87" s="40"/>
       <x:c r="G87" s="50"/>
-      <x:c r="H87"/>
-      <x:c r="I87"/>
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="40"/>
@@ -1615,8 +1381,6 @@
       <x:c r="E88" s="46"/>
       <x:c r="F88" s="40"/>
       <x:c r="G88" s="50"/>
-      <x:c r="H88"/>
-      <x:c r="I88"/>
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="40"/>
@@ -1626,8 +1390,6 @@
       <x:c r="E89" s="46"/>
       <x:c r="F89" s="40"/>
       <x:c r="G89" s="50"/>
-      <x:c r="H89"/>
-      <x:c r="I89"/>
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="40"/>
@@ -1637,8 +1399,6 @@
       <x:c r="E90" s="46"/>
       <x:c r="F90" s="40"/>
       <x:c r="G90" s="50"/>
-      <x:c r="H90"/>
-      <x:c r="I90"/>
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="40"/>
@@ -1648,8 +1408,6 @@
       <x:c r="E91" s="46"/>
       <x:c r="F91" s="40"/>
       <x:c r="G91" s="50"/>
-      <x:c r="H91"/>
-      <x:c r="I91"/>
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="40"/>
@@ -1659,8 +1417,6 @@
       <x:c r="E92" s="46"/>
       <x:c r="F92" s="40"/>
       <x:c r="G92" s="50"/>
-      <x:c r="H92"/>
-      <x:c r="I92"/>
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="40"/>
@@ -1670,8 +1426,6 @@
       <x:c r="E93" s="46"/>
       <x:c r="F93" s="40"/>
       <x:c r="G93" s="50"/>
-      <x:c r="H93"/>
-      <x:c r="I93"/>
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="40"/>
@@ -1681,8 +1435,6 @@
       <x:c r="E94" s="46"/>
       <x:c r="F94" s="40"/>
       <x:c r="G94" s="50"/>
-      <x:c r="H94"/>
-      <x:c r="I94"/>
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="40"/>
@@ -1692,8 +1444,6 @@
       <x:c r="E95" s="46"/>
       <x:c r="F95" s="40"/>
       <x:c r="G95" s="50"/>
-      <x:c r="H95"/>
-      <x:c r="I95"/>
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="40"/>
@@ -1703,8 +1453,6 @@
       <x:c r="E96" s="46"/>
       <x:c r="F96" s="40"/>
       <x:c r="G96" s="50"/>
-      <x:c r="H96"/>
-      <x:c r="I96"/>
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="40"/>
@@ -1714,8 +1462,6 @@
       <x:c r="E97" s="46"/>
       <x:c r="F97" s="40"/>
       <x:c r="G97" s="50"/>
-      <x:c r="H97"/>
-      <x:c r="I97"/>
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="40"/>
@@ -1725,8 +1471,6 @@
       <x:c r="E98" s="46"/>
       <x:c r="F98" s="40"/>
       <x:c r="G98" s="50"/>
-      <x:c r="H98"/>
-      <x:c r="I98"/>
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="40"/>
@@ -1736,8 +1480,6 @@
       <x:c r="E99" s="46"/>
       <x:c r="F99" s="40"/>
       <x:c r="G99" s="50"/>
-      <x:c r="H99"/>
-      <x:c r="I99"/>
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="40"/>
@@ -1747,8 +1489,6 @@
       <x:c r="E100" s="46"/>
       <x:c r="F100" s="40"/>
       <x:c r="G100" s="50"/>
-      <x:c r="H100"/>
-      <x:c r="I100"/>
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="40"/>
@@ -1758,8 +1498,6 @@
       <x:c r="E101" s="46"/>
       <x:c r="F101" s="40"/>
       <x:c r="G101" s="50"/>
-      <x:c r="H101"/>
-      <x:c r="I101"/>
     </x:row>
     <x:row r="102" ht="23" customHeight="1">
       <x:c r="A102" s="40"/>
@@ -1769,8 +1507,6 @@
       <x:c r="E102" s="46"/>
       <x:c r="F102" s="40"/>
       <x:c r="G102" s="50"/>
-      <x:c r="H102"/>
-      <x:c r="I102"/>
     </x:row>
     <x:row r="103" ht="23" customHeight="1">
       <x:c r="A103" s="40"/>
@@ -1780,8 +1516,6 @@
       <x:c r="E103" s="46"/>
       <x:c r="F103" s="40"/>
       <x:c r="G103" s="50"/>
-      <x:c r="H103"/>
-      <x:c r="I103"/>
     </x:row>
     <x:row r="104" ht="23" customHeight="1">
       <x:c r="A104" s="40"/>
@@ -1791,8 +1525,6 @@
       <x:c r="E104" s="46"/>
       <x:c r="F104" s="40"/>
       <x:c r="G104" s="50"/>
-      <x:c r="H104"/>
-      <x:c r="I104"/>
     </x:row>
     <x:row r="105" ht="23" customHeight="1">
       <x:c r="A105" s="40"/>
@@ -1802,8 +1534,6 @@
       <x:c r="E105" s="46"/>
       <x:c r="F105" s="40"/>
       <x:c r="G105" s="50"/>
-      <x:c r="H105"/>
-      <x:c r="I105"/>
     </x:row>
     <x:row r="106" ht="23" customHeight="1">
       <x:c r="A106" s="40"/>
@@ -1813,8 +1543,6 @@
       <x:c r="E106" s="46"/>
       <x:c r="F106" s="40"/>
       <x:c r="G106" s="50"/>
-      <x:c r="H106"/>
-      <x:c r="I106"/>
     </x:row>
     <x:row r="107" ht="23" customHeight="1">
       <x:c r="A107" s="40"/>
@@ -1824,8 +1552,6 @@
       <x:c r="E107" s="46"/>
       <x:c r="F107" s="40"/>
       <x:c r="G107" s="50"/>
-      <x:c r="H107"/>
-      <x:c r="I107"/>
     </x:row>
     <x:row r="108" ht="23" customHeight="1">
       <x:c r="A108" s="40"/>
@@ -1835,8 +1561,6 @@
       <x:c r="E108" s="46"/>
       <x:c r="F108" s="40"/>
       <x:c r="G108" s="50"/>
-      <x:c r="H108"/>
-      <x:c r="I108"/>
     </x:row>
     <x:row r="109" ht="23" customHeight="1">
       <x:c r="A109" s="40"/>
@@ -1846,8 +1570,6 @@
       <x:c r="E109" s="46"/>
       <x:c r="F109" s="40"/>
       <x:c r="G109" s="50"/>
-      <x:c r="H109"/>
-      <x:c r="I109"/>
     </x:row>
     <x:row r="110" ht="23" customHeight="1">
       <x:c r="A110" s="40"/>
@@ -1857,8 +1579,6 @@
       <x:c r="E110" s="46"/>
       <x:c r="F110" s="40"/>
       <x:c r="G110" s="50"/>
-      <x:c r="H110"/>
-      <x:c r="I110"/>
     </x:row>
     <x:row r="111" ht="23" customHeight="1">
       <x:c r="A111" s="40"/>
@@ -1868,8 +1588,6 @@
       <x:c r="E111" s="46"/>
       <x:c r="F111" s="40"/>
       <x:c r="G111" s="50"/>
-      <x:c r="H111"/>
-      <x:c r="I111"/>
     </x:row>
     <x:row r="112" ht="23" customHeight="1">
       <x:c r="A112" s="40"/>
@@ -1879,8 +1597,6 @@
       <x:c r="E112" s="46"/>
       <x:c r="F112" s="40"/>
       <x:c r="G112" s="50"/>
-      <x:c r="H112"/>
-      <x:c r="I112"/>
     </x:row>
     <x:row r="113" ht="23" customHeight="1">
       <x:c r="A113" s="40"/>
@@ -1890,8 +1606,6 @@
       <x:c r="E113" s="46"/>
       <x:c r="F113" s="40"/>
       <x:c r="G113" s="50"/>
-      <x:c r="H113"/>
-      <x:c r="I113"/>
     </x:row>
     <x:row r="114" ht="23" customHeight="1">
       <x:c r="A114" s="40"/>
@@ -1901,8 +1615,6 @@
       <x:c r="E114" s="46"/>
       <x:c r="F114" s="40"/>
       <x:c r="G114" s="50"/>
-      <x:c r="H114"/>
-      <x:c r="I114"/>
     </x:row>
     <x:row r="115" ht="23" customHeight="1">
       <x:c r="A115" s="40"/>
@@ -1912,8 +1624,6 @@
       <x:c r="E115" s="46"/>
       <x:c r="F115" s="40"/>
       <x:c r="G115" s="50"/>
-      <x:c r="H115"/>
-      <x:c r="I115"/>
     </x:row>
     <x:row r="116" ht="23" customHeight="1">
       <x:c r="A116" s="40"/>
@@ -1923,8 +1633,6 @@
       <x:c r="E116" s="46"/>
       <x:c r="F116" s="40"/>
       <x:c r="G116" s="50"/>
-      <x:c r="H116"/>
-      <x:c r="I116"/>
     </x:row>
     <x:row r="117" ht="23" customHeight="1">
       <x:c r="A117" s="40"/>
@@ -1934,8 +1642,6 @@
       <x:c r="E117" s="46"/>
       <x:c r="F117" s="40"/>
       <x:c r="G117" s="50"/>
-      <x:c r="H117"/>
-      <x:c r="I117"/>
     </x:row>
     <x:row r="118" ht="23" customHeight="1">
       <x:c r="A118" s="40"/>
@@ -1945,8 +1651,6 @@
       <x:c r="E118" s="46"/>
       <x:c r="F118" s="40"/>
       <x:c r="G118" s="50"/>
-      <x:c r="H118"/>
-      <x:c r="I118"/>
     </x:row>
     <x:row r="119" ht="23" customHeight="1">
       <x:c r="A119" s="40"/>
@@ -1956,8 +1660,6 @@
       <x:c r="E119" s="46"/>
       <x:c r="F119" s="40"/>
       <x:c r="G119" s="50"/>
-      <x:c r="H119"/>
-      <x:c r="I119"/>
     </x:row>
     <x:row r="120" ht="23" customHeight="1">
       <x:c r="A120" s="40"/>
@@ -1967,8 +1669,6 @@
       <x:c r="E120" s="46"/>
       <x:c r="F120" s="40"/>
       <x:c r="G120" s="50"/>
-      <x:c r="H120"/>
-      <x:c r="I120"/>
     </x:row>
     <x:row r="121" ht="23" customHeight="1">
       <x:c r="A121" s="40"/>
@@ -1978,8 +1678,6 @@
       <x:c r="E121" s="46"/>
       <x:c r="F121" s="40"/>
       <x:c r="G121" s="50"/>
-      <x:c r="H121"/>
-      <x:c r="I121"/>
     </x:row>
     <x:row r="122" ht="23" customHeight="1">
       <x:c r="A122" s="40"/>
@@ -1989,8 +1687,6 @@
       <x:c r="E122" s="46"/>
       <x:c r="F122" s="40"/>
       <x:c r="G122" s="50"/>
-      <x:c r="H122"/>
-      <x:c r="I122"/>
     </x:row>
     <x:row r="123" ht="23" customHeight="1">
       <x:c r="A123" s="40"/>
@@ -2000,8 +1696,6 @@
       <x:c r="E123" s="46"/>
       <x:c r="F123" s="40"/>
       <x:c r="G123" s="50"/>
-      <x:c r="H123"/>
-      <x:c r="I123"/>
     </x:row>
     <x:row r="124" ht="23" customHeight="1">
       <x:c r="A124" s="40"/>
@@ -2011,8 +1705,6 @@
       <x:c r="E124" s="46"/>
       <x:c r="F124" s="40"/>
       <x:c r="G124" s="50"/>
-      <x:c r="H124"/>
-      <x:c r="I124"/>
     </x:row>
     <x:row r="125" ht="23" customHeight="1">
       <x:c r="A125" s="40"/>
@@ -2022,8 +1714,6 @@
       <x:c r="E125" s="46"/>
       <x:c r="F125" s="40"/>
       <x:c r="G125" s="50"/>
-      <x:c r="H125"/>
-      <x:c r="I125"/>
     </x:row>
     <x:row r="126" ht="23" customHeight="1">
       <x:c r="A126" s="40"/>
@@ -2033,8 +1723,6 @@
       <x:c r="E126" s="46"/>
       <x:c r="F126" s="40"/>
       <x:c r="G126" s="50"/>
-      <x:c r="H126"/>
-      <x:c r="I126"/>
     </x:row>
     <x:row r="127" ht="23" customHeight="1">
       <x:c r="A127" s="40"/>
@@ -2044,8 +1732,6 @@
       <x:c r="E127" s="46"/>
       <x:c r="F127" s="40"/>
       <x:c r="G127" s="50"/>
-      <x:c r="H127"/>
-      <x:c r="I127"/>
     </x:row>
     <x:row r="128" ht="23" customHeight="1">
       <x:c r="A128" s="40"/>
@@ -2055,8 +1741,6 @@
       <x:c r="E128" s="46"/>
       <x:c r="F128" s="40"/>
       <x:c r="G128" s="50"/>
-      <x:c r="H128"/>
-      <x:c r="I128"/>
     </x:row>
     <x:row r="129" ht="23" customHeight="1">
       <x:c r="A129" s="40"/>
@@ -2066,8 +1750,6 @@
       <x:c r="E129" s="46"/>
       <x:c r="F129" s="40"/>
       <x:c r="G129" s="50"/>
-      <x:c r="H129"/>
-      <x:c r="I129"/>
     </x:row>
     <x:row r="130" ht="23" customHeight="1">
       <x:c r="A130" s="40"/>
@@ -2077,8 +1759,6 @@
       <x:c r="E130" s="46"/>
       <x:c r="F130" s="40"/>
       <x:c r="G130" s="50"/>
-      <x:c r="H130"/>
-      <x:c r="I130"/>
     </x:row>
     <x:row r="131" ht="23" customHeight="1">
       <x:c r="A131" s="40"/>
@@ -2088,8 +1768,6 @@
       <x:c r="E131" s="46"/>
       <x:c r="F131" s="40"/>
       <x:c r="G131" s="50"/>
-      <x:c r="H131"/>
-      <x:c r="I131"/>
     </x:row>
     <x:row r="132" ht="23" customHeight="1">
       <x:c r="A132" s="40"/>
@@ -2099,8 +1777,6 @@
       <x:c r="E132" s="46"/>
       <x:c r="F132" s="40"/>
       <x:c r="G132" s="50"/>
-      <x:c r="H132"/>
-      <x:c r="I132"/>
     </x:row>
     <x:row r="133" ht="23" customHeight="1">
       <x:c r="A133" s="40"/>
@@ -2110,8 +1786,6 @@
       <x:c r="E133" s="46"/>
       <x:c r="F133" s="40"/>
       <x:c r="G133" s="50"/>
-      <x:c r="H133"/>
-      <x:c r="I133"/>
     </x:row>
     <x:row r="134" ht="23" customHeight="1">
       <x:c r="A134" s="40"/>
@@ -2121,8 +1795,6 @@
       <x:c r="E134" s="46"/>
       <x:c r="F134" s="40"/>
       <x:c r="G134" s="50"/>
-      <x:c r="H134"/>
-      <x:c r="I134"/>
     </x:row>
     <x:row r="135" ht="23" customHeight="1">
       <x:c r="A135" s="40"/>
@@ -2132,8 +1804,6 @@
       <x:c r="E135" s="46"/>
       <x:c r="F135" s="40"/>
       <x:c r="G135" s="50"/>
-      <x:c r="H135"/>
-      <x:c r="I135"/>
     </x:row>
     <x:row r="136" ht="23" customHeight="1">
       <x:c r="A136" s="40"/>
@@ -2143,8 +1813,6 @@
       <x:c r="E136" s="46"/>
       <x:c r="F136" s="40"/>
       <x:c r="G136" s="50"/>
-      <x:c r="H136"/>
-      <x:c r="I136"/>
     </x:row>
     <x:row r="137" ht="23" customHeight="1">
       <x:c r="A137" s="40"/>
@@ -2154,8 +1822,6 @@
       <x:c r="E137" s="46"/>
       <x:c r="F137" s="40"/>
       <x:c r="G137" s="50"/>
-      <x:c r="H137"/>
-      <x:c r="I137"/>
     </x:row>
     <x:row r="138" ht="23" customHeight="1">
       <x:c r="A138" s="40"/>
@@ -2165,8 +1831,6 @@
       <x:c r="E138" s="46"/>
       <x:c r="F138" s="40"/>
       <x:c r="G138" s="50"/>
-      <x:c r="H138"/>
-      <x:c r="I138"/>
     </x:row>
     <x:row r="139" ht="23" customHeight="1">
       <x:c r="A139" s="40"/>
@@ -2176,8 +1840,6 @@
       <x:c r="E139" s="46"/>
       <x:c r="F139" s="40"/>
       <x:c r="G139" s="50"/>
-      <x:c r="H139"/>
-      <x:c r="I139"/>
     </x:row>
     <x:row r="140" ht="23" customHeight="1">
       <x:c r="A140" s="40"/>
@@ -2187,8 +1849,6 @@
       <x:c r="E140" s="46"/>
       <x:c r="F140" s="40"/>
       <x:c r="G140" s="50"/>
-      <x:c r="H140"/>
-      <x:c r="I140"/>
     </x:row>
     <x:row r="141" ht="23" customHeight="1">
       <x:c r="A141" s="40"/>
@@ -2198,8 +1858,6 @@
       <x:c r="E141" s="46"/>
       <x:c r="F141" s="40"/>
       <x:c r="G141" s="50"/>
-      <x:c r="H141"/>
-      <x:c r="I141"/>
     </x:row>
     <x:row r="142" ht="23" customHeight="1">
       <x:c r="A142" s="40"/>
@@ -2209,8 +1867,6 @@
       <x:c r="E142" s="46"/>
       <x:c r="F142" s="40"/>
       <x:c r="G142" s="50"/>
-      <x:c r="H142"/>
-      <x:c r="I142"/>
     </x:row>
     <x:row r="143" ht="23" customHeight="1">
       <x:c r="A143" s="40"/>
@@ -2220,8 +1876,6 @@
       <x:c r="E143" s="46"/>
       <x:c r="F143" s="40"/>
       <x:c r="G143" s="50"/>
-      <x:c r="H143"/>
-      <x:c r="I143"/>
     </x:row>
     <x:row r="144" ht="23" customHeight="1">
       <x:c r="A144" s="40"/>
@@ -2231,8 +1885,6 @@
       <x:c r="E144" s="46"/>
       <x:c r="F144" s="40"/>
       <x:c r="G144" s="50"/>
-      <x:c r="H144"/>
-      <x:c r="I144"/>
     </x:row>
     <x:row r="145" ht="23" customHeight="1">
       <x:c r="A145" s="40"/>
@@ -2242,8 +1894,6 @@
       <x:c r="E145" s="46"/>
       <x:c r="F145" s="40"/>
       <x:c r="G145" s="50"/>
-      <x:c r="H145"/>
-      <x:c r="I145"/>
     </x:row>
     <x:row r="146" ht="23" customHeight="1">
       <x:c r="A146" s="40"/>
@@ -2253,8 +1903,6 @@
       <x:c r="E146" s="46"/>
       <x:c r="F146" s="40"/>
       <x:c r="G146" s="50"/>
-      <x:c r="H146"/>
-      <x:c r="I146"/>
     </x:row>
     <x:row r="147" ht="23" customHeight="1">
       <x:c r="A147" s="40"/>
@@ -2264,8 +1912,6 @@
       <x:c r="E147" s="46"/>
       <x:c r="F147" s="40"/>
       <x:c r="G147" s="50"/>
-      <x:c r="H147"/>
-      <x:c r="I147"/>
     </x:row>
     <x:row r="148" ht="23" customHeight="1">
       <x:c r="A148" s="40"/>
@@ -2275,8 +1921,6 @@
       <x:c r="E148" s="46"/>
       <x:c r="F148" s="40"/>
       <x:c r="G148" s="50"/>
-      <x:c r="H148"/>
-      <x:c r="I148"/>
     </x:row>
     <x:row r="149" ht="23" customHeight="1">
       <x:c r="A149" s="40"/>
@@ -2286,8 +1930,6 @@
       <x:c r="E149" s="46"/>
       <x:c r="F149" s="40"/>
       <x:c r="G149" s="50"/>
-      <x:c r="H149"/>
-      <x:c r="I149"/>
     </x:row>
     <x:row r="150" ht="23" customHeight="1">
       <x:c r="A150" s="40"/>
@@ -2297,8 +1939,6 @@
       <x:c r="E150" s="46"/>
       <x:c r="F150" s="40"/>
       <x:c r="G150" s="50"/>
-      <x:c r="H150"/>
-      <x:c r="I150"/>
     </x:row>
     <x:row r="151" ht="23" customHeight="1">
       <x:c r="A151" s="40"/>
@@ -2308,8 +1948,6 @@
       <x:c r="E151" s="46"/>
       <x:c r="F151" s="40"/>
       <x:c r="G151" s="50"/>
-      <x:c r="H151"/>
-      <x:c r="I151"/>
     </x:row>
     <x:row r="152" ht="23" customHeight="1">
       <x:c r="A152" s="40"/>
@@ -2319,8 +1957,6 @@
       <x:c r="E152" s="46"/>
       <x:c r="F152" s="40"/>
       <x:c r="G152" s="50"/>
-      <x:c r="H152"/>
-      <x:c r="I152"/>
     </x:row>
     <x:row r="153" ht="23" customHeight="1">
       <x:c r="A153" s="40"/>
@@ -2330,8 +1966,6 @@
       <x:c r="E153" s="46"/>
       <x:c r="F153" s="40"/>
       <x:c r="G153" s="50"/>
-      <x:c r="H153"/>
-      <x:c r="I153"/>
     </x:row>
     <x:row r="154" ht="23" customHeight="1">
       <x:c r="A154" s="40"/>
@@ -2341,8 +1975,6 @@
       <x:c r="E154" s="46"/>
       <x:c r="F154" s="40"/>
       <x:c r="G154" s="50"/>
-      <x:c r="H154"/>
-      <x:c r="I154"/>
     </x:row>
     <x:row r="155" ht="23" customHeight="1">
       <x:c r="A155" s="40"/>
@@ -2352,8 +1984,6 @@
       <x:c r="E155" s="46"/>
       <x:c r="F155" s="40"/>
       <x:c r="G155" s="50"/>
-      <x:c r="H155"/>
-      <x:c r="I155"/>
     </x:row>
     <x:row r="156" ht="23" customHeight="1">
       <x:c r="A156" s="40"/>
@@ -2363,8 +1993,6 @@
       <x:c r="E156" s="46"/>
       <x:c r="F156" s="40"/>
       <x:c r="G156" s="50"/>
-      <x:c r="H156"/>
-      <x:c r="I156"/>
     </x:row>
     <x:row r="157" ht="23" customHeight="1">
       <x:c r="A157" s="40"/>
@@ -2374,8 +2002,6 @@
       <x:c r="E157" s="46"/>
       <x:c r="F157" s="40"/>
       <x:c r="G157" s="50"/>
-      <x:c r="H157"/>
-      <x:c r="I157"/>
     </x:row>
     <x:row r="158" ht="23" customHeight="1">
       <x:c r="A158" s="40"/>
@@ -2385,8 +2011,6 @@
       <x:c r="E158" s="46"/>
       <x:c r="F158" s="40"/>
       <x:c r="G158" s="50"/>
-      <x:c r="H158"/>
-      <x:c r="I158"/>
     </x:row>
     <x:row r="159" ht="23" customHeight="1">
       <x:c r="A159" s="40"/>
@@ -2396,8 +2020,6 @@
       <x:c r="E159" s="46"/>
       <x:c r="F159" s="40"/>
       <x:c r="G159" s="50"/>
-      <x:c r="H159"/>
-      <x:c r="I159"/>
     </x:row>
     <x:row r="160" ht="23" customHeight="1">
       <x:c r="A160" s="40"/>
@@ -2407,8 +2029,6 @@
       <x:c r="E160" s="46"/>
       <x:c r="F160" s="40"/>
       <x:c r="G160" s="50"/>
-      <x:c r="H160"/>
-      <x:c r="I160"/>
     </x:row>
     <x:row r="161" ht="23" customHeight="1">
       <x:c r="A161" s="40"/>
@@ -2418,8 +2038,6 @@
       <x:c r="E161" s="46"/>
       <x:c r="F161" s="40"/>
       <x:c r="G161" s="50"/>
-      <x:c r="H161"/>
-      <x:c r="I161"/>
     </x:row>
     <x:row r="162" ht="23" customHeight="1">
       <x:c r="A162" s="40"/>
@@ -2429,8 +2047,6 @@
       <x:c r="E162" s="46"/>
       <x:c r="F162" s="40"/>
       <x:c r="G162" s="50"/>
-      <x:c r="H162"/>
-      <x:c r="I162"/>
     </x:row>
     <x:row r="163" ht="23" customHeight="1">
       <x:c r="A163" s="40"/>
@@ -2440,8 +2056,6 @@
       <x:c r="E163" s="46"/>
       <x:c r="F163" s="40"/>
       <x:c r="G163" s="50"/>
-      <x:c r="H163"/>
-      <x:c r="I163"/>
     </x:row>
     <x:row r="164" ht="23" customHeight="1">
       <x:c r="A164" s="40"/>
@@ -2451,8 +2065,6 @@
       <x:c r="E164" s="46"/>
       <x:c r="F164" s="40"/>
       <x:c r="G164" s="50"/>
-      <x:c r="H164"/>
-      <x:c r="I164"/>
     </x:row>
     <x:row r="165" ht="23" customHeight="1">
       <x:c r="A165" s="40"/>
@@ -2462,8 +2074,6 @@
       <x:c r="E165" s="46"/>
       <x:c r="F165" s="40"/>
       <x:c r="G165" s="50"/>
-      <x:c r="H165"/>
-      <x:c r="I165"/>
     </x:row>
     <x:row r="166" ht="23" customHeight="1">
       <x:c r="A166" s="40"/>
@@ -2473,8 +2083,6 @@
       <x:c r="E166" s="46"/>
       <x:c r="F166" s="40"/>
       <x:c r="G166" s="50"/>
-      <x:c r="H166"/>
-      <x:c r="I166"/>
     </x:row>
     <x:row r="167" ht="23" customHeight="1">
       <x:c r="A167" s="40"/>
@@ -2484,8 +2092,6 @@
       <x:c r="E167" s="46"/>
       <x:c r="F167" s="40"/>
       <x:c r="G167" s="50"/>
-      <x:c r="H167"/>
-      <x:c r="I167"/>
     </x:row>
     <x:row r="168" ht="23" customHeight="1">
       <x:c r="A168" s="40"/>
@@ -2495,8 +2101,6 @@
       <x:c r="E168" s="46"/>
       <x:c r="F168" s="40"/>
       <x:c r="G168" s="50"/>
-      <x:c r="H168"/>
-      <x:c r="I168"/>
     </x:row>
     <x:row r="169" ht="23" customHeight="1">
       <x:c r="A169" s="40"/>
@@ -2506,8 +2110,6 @@
       <x:c r="E169" s="46"/>
       <x:c r="F169" s="40"/>
       <x:c r="G169" s="50"/>
-      <x:c r="H169"/>
-      <x:c r="I169"/>
     </x:row>
     <x:row r="170" ht="23" customHeight="1">
       <x:c r="A170" s="40"/>
@@ -2517,8 +2119,6 @@
       <x:c r="E170" s="46"/>
       <x:c r="F170" s="40"/>
       <x:c r="G170" s="50"/>
-      <x:c r="H170"/>
-      <x:c r="I170"/>
     </x:row>
     <x:row r="171" ht="23" customHeight="1">
       <x:c r="A171" s="40"/>
@@ -2528,8 +2128,6 @@
       <x:c r="E171" s="46"/>
       <x:c r="F171" s="40"/>
       <x:c r="G171" s="50"/>
-      <x:c r="H171"/>
-      <x:c r="I171"/>
     </x:row>
     <x:row r="172" ht="23" customHeight="1">
       <x:c r="A172" s="40"/>
@@ -2539,8 +2137,6 @@
       <x:c r="E172" s="46"/>
       <x:c r="F172" s="40"/>
       <x:c r="G172" s="50"/>
-      <x:c r="H172"/>
-      <x:c r="I172"/>
     </x:row>
     <x:row r="173" ht="23" customHeight="1">
       <x:c r="A173" s="40"/>
@@ -2550,8 +2146,6 @@
       <x:c r="E173" s="46"/>
       <x:c r="F173" s="40"/>
       <x:c r="G173" s="50"/>
-      <x:c r="H173"/>
-      <x:c r="I173"/>
     </x:row>
     <x:row r="174" ht="23" customHeight="1">
       <x:c r="A174" s="40"/>
@@ -2561,8 +2155,6 @@
       <x:c r="E174" s="46"/>
       <x:c r="F174" s="40"/>
       <x:c r="G174" s="50"/>
-      <x:c r="H174"/>
-      <x:c r="I174"/>
     </x:row>
     <x:row r="175" ht="23" customHeight="1">
       <x:c r="A175" s="40"/>
@@ -2572,8 +2164,6 @@
       <x:c r="E175" s="46"/>
       <x:c r="F175" s="40"/>
       <x:c r="G175" s="50"/>
-      <x:c r="H175"/>
-      <x:c r="I175"/>
     </x:row>
     <x:row r="176" ht="23" customHeight="1">
       <x:c r="A176" s="40"/>
@@ -2583,8 +2173,6 @@
       <x:c r="E176" s="46"/>
       <x:c r="F176" s="40"/>
       <x:c r="G176" s="50"/>
-      <x:c r="H176"/>
-      <x:c r="I176"/>
     </x:row>
     <x:row r="177" ht="23" customHeight="1">
       <x:c r="A177" s="40"/>
@@ -2594,8 +2182,6 @@
       <x:c r="E177" s="46"/>
       <x:c r="F177" s="40"/>
       <x:c r="G177" s="50"/>
-      <x:c r="H177"/>
-      <x:c r="I177"/>
     </x:row>
     <x:row r="178" ht="23" customHeight="1">
       <x:c r="A178" s="40"/>
@@ -2605,8 +2191,6 @@
       <x:c r="E178" s="46"/>
       <x:c r="F178" s="40"/>
       <x:c r="G178" s="50"/>
-      <x:c r="H178"/>
-      <x:c r="I178"/>
     </x:row>
     <x:row r="179" ht="23" customHeight="1">
       <x:c r="A179" s="40"/>
@@ -2616,8 +2200,6 @@
       <x:c r="E179" s="46"/>
       <x:c r="F179" s="40"/>
       <x:c r="G179" s="50"/>
-      <x:c r="H179"/>
-      <x:c r="I179"/>
     </x:row>
     <x:row r="180" ht="23" customHeight="1">
       <x:c r="A180" s="40"/>
@@ -2627,8 +2209,6 @@
       <x:c r="E180" s="46"/>
       <x:c r="F180" s="40"/>
       <x:c r="G180" s="50"/>
-      <x:c r="H180"/>
-      <x:c r="I180"/>
     </x:row>
     <x:row r="181" ht="23" customHeight="1">
       <x:c r="A181" s="40"/>
@@ -2638,8 +2218,6 @@
       <x:c r="E181" s="46"/>
       <x:c r="F181" s="40"/>
       <x:c r="G181" s="50"/>
-      <x:c r="H181"/>
-      <x:c r="I181"/>
     </x:row>
     <x:row r="182" ht="23" customHeight="1">
       <x:c r="A182" s="40"/>
@@ -2649,8 +2227,6 @@
       <x:c r="E182" s="46"/>
       <x:c r="F182" s="40"/>
       <x:c r="G182" s="50"/>
-      <x:c r="H182"/>
-      <x:c r="I182"/>
     </x:row>
     <x:row r="183" ht="23" customHeight="1">
       <x:c r="A183" s="40"/>
@@ -2660,8 +2236,6 @@
       <x:c r="E183" s="46"/>
       <x:c r="F183" s="40"/>
       <x:c r="G183" s="50"/>
-      <x:c r="H183"/>
-      <x:c r="I183"/>
     </x:row>
     <x:row r="184" ht="23" customHeight="1">
       <x:c r="A184" s="40"/>
@@ -2671,8 +2245,6 @@
       <x:c r="E184" s="46"/>
       <x:c r="F184" s="40"/>
       <x:c r="G184" s="50"/>
-      <x:c r="H184"/>
-      <x:c r="I184"/>
     </x:row>
     <x:row r="185" ht="23" customHeight="1">
       <x:c r="A185" s="40"/>
@@ -2682,8 +2254,6 @@
       <x:c r="E185" s="46"/>
       <x:c r="F185" s="40"/>
       <x:c r="G185" s="50"/>
-      <x:c r="H185"/>
-      <x:c r="I185"/>
     </x:row>
     <x:row r="186" ht="23" customHeight="1">
       <x:c r="A186" s="40"/>
@@ -2693,8 +2263,6 @@
       <x:c r="E186" s="46"/>
       <x:c r="F186" s="40"/>
       <x:c r="G186" s="50"/>
-      <x:c r="H186"/>
-      <x:c r="I186"/>
     </x:row>
     <x:row r="187" ht="23" customHeight="1">
       <x:c r="A187" s="40"/>
@@ -2704,8 +2272,6 @@
       <x:c r="E187" s="46"/>
       <x:c r="F187" s="40"/>
       <x:c r="G187" s="50"/>
-      <x:c r="H187"/>
-      <x:c r="I187"/>
     </x:row>
     <x:row r="188" ht="23" customHeight="1">
       <x:c r="A188" s="40"/>
@@ -2715,8 +2281,6 @@
       <x:c r="E188" s="46"/>
       <x:c r="F188" s="40"/>
       <x:c r="G188" s="50"/>
-      <x:c r="H188"/>
-      <x:c r="I188"/>
     </x:row>
     <x:row r="189" ht="23" customHeight="1">
       <x:c r="A189" s="40"/>
@@ -2726,8 +2290,6 @@
       <x:c r="E189" s="46"/>
       <x:c r="F189" s="40"/>
       <x:c r="G189" s="50"/>
-      <x:c r="H189"/>
-      <x:c r="I189"/>
     </x:row>
     <x:row r="190" ht="23" customHeight="1">
       <x:c r="A190" s="40"/>
@@ -2737,8 +2299,6 @@
       <x:c r="E190" s="46"/>
       <x:c r="F190" s="40"/>
       <x:c r="G190" s="50"/>
-      <x:c r="H190"/>
-      <x:c r="I190"/>
     </x:row>
     <x:row r="191" ht="23" customHeight="1">
       <x:c r="A191" s="40"/>
@@ -2748,8 +2308,6 @@
       <x:c r="E191" s="46"/>
       <x:c r="F191" s="40"/>
       <x:c r="G191" s="50"/>
-      <x:c r="H191"/>
-      <x:c r="I191"/>
     </x:row>
     <x:row r="192" ht="23" customHeight="1">
       <x:c r="A192" s="40"/>
@@ -2759,8 +2317,6 @@
       <x:c r="E192" s="46"/>
       <x:c r="F192" s="40"/>
       <x:c r="G192" s="50"/>
-      <x:c r="H192"/>
-      <x:c r="I192"/>
     </x:row>
     <x:row r="193" ht="23" customHeight="1">
       <x:c r="A193" s="40"/>
@@ -2770,8 +2326,6 @@
       <x:c r="E193" s="46"/>
       <x:c r="F193" s="40"/>
       <x:c r="G193" s="50"/>
-      <x:c r="H193"/>
-      <x:c r="I193"/>
     </x:row>
     <x:row r="194" ht="23" customHeight="1">
       <x:c r="A194" s="40"/>
@@ -2781,8 +2335,6 @@
       <x:c r="E194" s="46"/>
       <x:c r="F194" s="40"/>
       <x:c r="G194" s="50"/>
-      <x:c r="H194"/>
-      <x:c r="I194"/>
     </x:row>
     <x:row r="195" ht="23" customHeight="1">
       <x:c r="A195" s="40"/>
@@ -2792,8 +2344,6 @@
       <x:c r="E195" s="46"/>
       <x:c r="F195" s="40"/>
       <x:c r="G195" s="50"/>
-      <x:c r="H195"/>
-      <x:c r="I195"/>
     </x:row>
     <x:row r="196" ht="23" customHeight="1">
       <x:c r="A196" s="40"/>
@@ -2803,8 +2353,6 @@
       <x:c r="E196" s="46"/>
       <x:c r="F196" s="40"/>
       <x:c r="G196" s="50"/>
-      <x:c r="H196"/>
-      <x:c r="I196"/>
     </x:row>
     <x:row r="197" ht="23" customHeight="1">
       <x:c r="A197" s="40"/>
@@ -2814,8 +2362,6 @@
       <x:c r="E197" s="46"/>
       <x:c r="F197" s="40"/>
       <x:c r="G197" s="50"/>
-      <x:c r="H197"/>
-      <x:c r="I197"/>
     </x:row>
     <x:row r="198" ht="23" customHeight="1">
       <x:c r="A198" s="40"/>
@@ -2825,8 +2371,6 @@
       <x:c r="E198" s="46"/>
       <x:c r="F198" s="40"/>
       <x:c r="G198" s="50"/>
-      <x:c r="H198"/>
-      <x:c r="I198"/>
     </x:row>
     <x:row r="199" ht="23" customHeight="1">
       <x:c r="A199" s="40"/>
@@ -2836,8 +2380,6 @@
       <x:c r="E199" s="46"/>
       <x:c r="F199" s="40"/>
       <x:c r="G199" s="50"/>
-      <x:c r="H199"/>
-      <x:c r="I199"/>
     </x:row>
     <x:row r="200" ht="23" customHeight="1">
       <x:c r="A200" s="40"/>
@@ -2847,8 +2389,6 @@
       <x:c r="E200" s="46"/>
       <x:c r="F200" s="40"/>
       <x:c r="G200" s="50"/>
-      <x:c r="H200"/>
-      <x:c r="I200"/>
     </x:row>
     <x:row r="201" ht="23" customHeight="1">
       <x:c r="A201" s="40"/>
@@ -2858,8 +2398,6 @@
       <x:c r="E201" s="46"/>
       <x:c r="F201" s="40"/>
       <x:c r="G201" s="50"/>
-      <x:c r="H201"/>
-      <x:c r="I201"/>
     </x:row>
     <x:row r="202" ht="23" customHeight="1">
       <x:c r="A202" s="40"/>
@@ -2869,8 +2407,6 @@
       <x:c r="E202" s="46"/>
       <x:c r="F202" s="40"/>
       <x:c r="G202" s="50"/>
-      <x:c r="H202"/>
-      <x:c r="I202"/>
     </x:row>
     <x:row r="203" ht="23" customHeight="1">
       <x:c r="A203" s="40"/>
@@ -2880,8 +2416,6 @@
       <x:c r="E203" s="46"/>
       <x:c r="F203" s="40"/>
       <x:c r="G203" s="50"/>
-      <x:c r="H203"/>
-      <x:c r="I203"/>
     </x:row>
     <x:row r="204" ht="23" customHeight="1">
       <x:c r="A204" s="40"/>
@@ -2891,8 +2425,6 @@
       <x:c r="E204" s="46"/>
       <x:c r="F204" s="40"/>
       <x:c r="G204" s="50"/>
-      <x:c r="H204"/>
-      <x:c r="I204"/>
     </x:row>
     <x:row r="205" ht="23" customHeight="1">
       <x:c r="A205" s="40"/>
@@ -2902,8 +2434,6 @@
       <x:c r="E205" s="46"/>
       <x:c r="F205" s="40"/>
       <x:c r="G205" s="50"/>
-      <x:c r="H205"/>
-      <x:c r="I205"/>
     </x:row>
     <x:row r="206" ht="23" customHeight="1">
       <x:c r="A206" s="40"/>
